--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302737</v>
+        <v>122302746</v>
       </c>
       <c r="B2" t="n">
         <v>78645</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455267</v>
+        <v>455138</v>
       </c>
       <c r="R2" t="n">
-        <v>6812474</v>
+        <v>6812473</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302751</v>
+        <v>122302538</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>79263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454998</v>
+        <v>455290</v>
       </c>
       <c r="R3" t="n">
-        <v>6812459</v>
+        <v>6812727</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302604</v>
+        <v>122302659</v>
       </c>
       <c r="B4" t="n">
         <v>78645</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455405</v>
+        <v>455293</v>
       </c>
       <c r="R4" t="n">
-        <v>6812359</v>
+        <v>6812728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302746</v>
+        <v>122302655</v>
       </c>
       <c r="B5" t="n">
         <v>78645</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455138</v>
+        <v>455201</v>
       </c>
       <c r="R5" t="n">
-        <v>6812473</v>
+        <v>6812767</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302750</v>
+        <v>122302671</v>
       </c>
       <c r="B6" t="n">
         <v>78645</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455083</v>
+        <v>455616</v>
       </c>
       <c r="R6" t="n">
-        <v>6812476</v>
+        <v>6812570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302666</v>
+        <v>122302748</v>
       </c>
       <c r="B7" t="n">
         <v>78645</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455428</v>
+        <v>455119</v>
       </c>
       <c r="R7" t="n">
-        <v>6812747</v>
+        <v>6812489</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302725</v>
+        <v>122302667</v>
       </c>
       <c r="B8" t="n">
         <v>78645</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455413</v>
+        <v>455438</v>
       </c>
       <c r="R8" t="n">
-        <v>6812371</v>
+        <v>6812744</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302553</v>
+        <v>122302579</v>
       </c>
       <c r="B9" t="n">
-        <v>79234</v>
+        <v>78382</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455736</v>
+        <v>455212</v>
       </c>
       <c r="R9" t="n">
-        <v>6812556</v>
+        <v>6812763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302655</v>
+        <v>122302584</v>
       </c>
       <c r="B10" t="n">
-        <v>78645</v>
+        <v>78382</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455201</v>
+        <v>455165</v>
       </c>
       <c r="R10" t="n">
-        <v>6812767</v>
+        <v>6812417</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302744</v>
+        <v>122302753</v>
       </c>
       <c r="B11" t="n">
         <v>78645</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455165</v>
+        <v>454977</v>
       </c>
       <c r="R11" t="n">
-        <v>6812443</v>
+        <v>6812451</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302657</v>
+        <v>122302747</v>
       </c>
       <c r="B12" t="n">
         <v>78645</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455243</v>
+        <v>455137</v>
       </c>
       <c r="R12" t="n">
-        <v>6812747</v>
+        <v>6812474</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302656</v>
+        <v>122302650</v>
       </c>
       <c r="B13" t="n">
         <v>78645</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455229</v>
+        <v>455089</v>
       </c>
       <c r="R13" t="n">
-        <v>6812759</v>
+        <v>6812828</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302538</v>
+        <v>122302604</v>
       </c>
       <c r="B14" t="n">
-        <v>79263</v>
+        <v>78645</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455290</v>
+        <v>455405</v>
       </c>
       <c r="R14" t="n">
-        <v>6812727</v>
+        <v>6812359</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302585</v>
+        <v>122302725</v>
       </c>
       <c r="B15" t="n">
-        <v>78382</v>
+        <v>78645</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454995</v>
+        <v>455413</v>
       </c>
       <c r="R15" t="n">
-        <v>6812454</v>
+        <v>6812371</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302650</v>
+        <v>122302749</v>
       </c>
       <c r="B16" t="n">
         <v>78645</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455089</v>
+        <v>455098</v>
       </c>
       <c r="R16" t="n">
-        <v>6812828</v>
+        <v>6812474</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302665</v>
+        <v>122302727</v>
       </c>
       <c r="B17" t="n">
         <v>78645</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455420</v>
+        <v>455408</v>
       </c>
       <c r="R17" t="n">
-        <v>6812744</v>
+        <v>6812407</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302754</v>
+        <v>122302751</v>
       </c>
       <c r="B18" t="n">
         <v>78645</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454970</v>
+        <v>454998</v>
       </c>
       <c r="R18" t="n">
-        <v>6812456</v>
+        <v>6812459</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302584</v>
+        <v>122302750</v>
       </c>
       <c r="B19" t="n">
-        <v>78382</v>
+        <v>78645</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455165</v>
+        <v>455083</v>
       </c>
       <c r="R19" t="n">
-        <v>6812417</v>
+        <v>6812476</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302605</v>
+        <v>122302736</v>
       </c>
       <c r="B20" t="n">
         <v>78645</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455043</v>
+        <v>455295</v>
       </c>
       <c r="R20" t="n">
-        <v>6812499</v>
+        <v>6812491</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302673</v>
+        <v>122302658</v>
       </c>
       <c r="B21" t="n">
         <v>78645</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455747</v>
+        <v>455259</v>
       </c>
       <c r="R21" t="n">
-        <v>6812550</v>
+        <v>6812731</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302652</v>
+        <v>122302537</v>
       </c>
       <c r="B22" t="n">
-        <v>78645</v>
+        <v>79263</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455165</v>
+        <v>455203</v>
       </c>
       <c r="R22" t="n">
-        <v>6812792</v>
+        <v>6812760</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302537</v>
+        <v>122302668</v>
       </c>
       <c r="B23" t="n">
-        <v>79263</v>
+        <v>78645</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455203</v>
+        <v>455485</v>
       </c>
       <c r="R23" t="n">
-        <v>6812760</v>
+        <v>6812754</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302671</v>
+        <v>122302553</v>
       </c>
       <c r="B24" t="n">
-        <v>78645</v>
+        <v>79234</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455616</v>
+        <v>455736</v>
       </c>
       <c r="R24" t="n">
-        <v>6812570</v>
+        <v>6812556</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302748</v>
+        <v>122302726</v>
       </c>
       <c r="B25" t="n">
         <v>78645</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455119</v>
+        <v>455407</v>
       </c>
       <c r="R25" t="n">
-        <v>6812489</v>
+        <v>6812392</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3123,7 +3123,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302658</v>
+        <v>122302654</v>
       </c>
       <c r="B26" t="n">
         <v>78645</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455259</v>
+        <v>455187</v>
       </c>
       <c r="R26" t="n">
-        <v>6812731</v>
+        <v>6812780</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,7 +3225,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302653</v>
+        <v>122302673</v>
       </c>
       <c r="B27" t="n">
         <v>78645</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455173</v>
+        <v>455747</v>
       </c>
       <c r="R27" t="n">
-        <v>6812786</v>
+        <v>6812550</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302651</v>
+        <v>122302603</v>
       </c>
       <c r="B28" t="n">
         <v>78645</v>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455119</v>
+        <v>455413</v>
       </c>
       <c r="R28" t="n">
-        <v>6812817</v>
+        <v>6812351</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3429,7 +3429,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122302654</v>
+        <v>122302666</v>
       </c>
       <c r="B29" t="n">
         <v>78645</v>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455187</v>
+        <v>455428</v>
       </c>
       <c r="R29" t="n">
-        <v>6812780</v>
+        <v>6812747</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302672</v>
+        <v>122302773</v>
       </c>
       <c r="B30" t="n">
-        <v>78645</v>
+        <v>78029</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455638</v>
+        <v>454992</v>
       </c>
       <c r="R30" t="n">
-        <v>6812544</v>
+        <v>6812487</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302749</v>
+        <v>122302594</v>
       </c>
       <c r="B31" t="n">
-        <v>78645</v>
+        <v>78381</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455098</v>
+        <v>455177</v>
       </c>
       <c r="R31" t="n">
-        <v>6812474</v>
+        <v>6812448</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302743</v>
+        <v>122302585</v>
       </c>
       <c r="B32" t="n">
-        <v>78645</v>
+        <v>78382</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455165</v>
+        <v>454995</v>
       </c>
       <c r="R32" t="n">
-        <v>6812417</v>
+        <v>6812454</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122302727</v>
+        <v>122302743</v>
       </c>
       <c r="B33" t="n">
         <v>78645</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455408</v>
+        <v>455165</v>
       </c>
       <c r="R33" t="n">
-        <v>6812407</v>
+        <v>6812417</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122302583</v>
+        <v>122302552</v>
       </c>
       <c r="B34" t="n">
-        <v>78382</v>
+        <v>78679</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455177</v>
+        <v>455409</v>
       </c>
       <c r="R34" t="n">
-        <v>6812448</v>
+        <v>6812375</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122302752</v>
+        <v>122302744</v>
       </c>
       <c r="B35" t="n">
         <v>78645</v>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454985</v>
+        <v>455165</v>
       </c>
       <c r="R35" t="n">
-        <v>6812455</v>
+        <v>6812443</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122302753</v>
+        <v>122302651</v>
       </c>
       <c r="B36" t="n">
         <v>78645</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454977</v>
+        <v>455119</v>
       </c>
       <c r="R36" t="n">
-        <v>6812451</v>
+        <v>6812817</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302736</v>
+        <v>122302605</v>
       </c>
       <c r="B37" t="n">
         <v>78645</v>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455295</v>
+        <v>455043</v>
       </c>
       <c r="R37" t="n">
-        <v>6812491</v>
+        <v>6812499</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302668</v>
+        <v>122302724</v>
       </c>
       <c r="B38" t="n">
         <v>78645</v>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455485</v>
+        <v>455449</v>
       </c>
       <c r="R38" t="n">
-        <v>6812754</v>
+        <v>6812352</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4449,7 +4449,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302670</v>
+        <v>122302657</v>
       </c>
       <c r="B39" t="n">
         <v>78645</v>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455615</v>
+        <v>455243</v>
       </c>
       <c r="R39" t="n">
-        <v>6812587</v>
+        <v>6812747</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122302674</v>
+        <v>122302752</v>
       </c>
       <c r="B40" t="n">
         <v>78645</v>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455758</v>
+        <v>454985</v>
       </c>
       <c r="R40" t="n">
-        <v>6812559</v>
+        <v>6812455</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,7 +4653,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302724</v>
+        <v>122302665</v>
       </c>
       <c r="B41" t="n">
         <v>78645</v>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455449</v>
+        <v>455420</v>
       </c>
       <c r="R41" t="n">
-        <v>6812352</v>
+        <v>6812744</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4755,7 +4755,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302659</v>
+        <v>122302745</v>
       </c>
       <c r="B42" t="n">
         <v>78645</v>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455293</v>
+        <v>455154</v>
       </c>
       <c r="R42" t="n">
-        <v>6812728</v>
+        <v>6812449</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302773</v>
+        <v>122302754</v>
       </c>
       <c r="B43" t="n">
-        <v>78029</v>
+        <v>78645</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454992</v>
+        <v>454970</v>
       </c>
       <c r="R43" t="n">
-        <v>6812487</v>
+        <v>6812456</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302552</v>
+        <v>122302653</v>
       </c>
       <c r="B44" t="n">
-        <v>78679</v>
+        <v>78645</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455409</v>
+        <v>455173</v>
       </c>
       <c r="R44" t="n">
-        <v>6812375</v>
+        <v>6812786</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5061,7 +5061,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302726</v>
+        <v>122302652</v>
       </c>
       <c r="B45" t="n">
         <v>78645</v>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455407</v>
+        <v>455165</v>
       </c>
       <c r="R45" t="n">
-        <v>6812392</v>
+        <v>6812792</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5163,10 +5163,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122302747</v>
+        <v>122302583</v>
       </c>
       <c r="B46" t="n">
-        <v>78645</v>
+        <v>78382</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5179,21 +5179,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455137</v>
+        <v>455177</v>
       </c>
       <c r="R46" t="n">
-        <v>6812474</v>
+        <v>6812448</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122302745</v>
+        <v>122302672</v>
       </c>
       <c r="B47" t="n">
         <v>78645</v>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455154</v>
+        <v>455638</v>
       </c>
       <c r="R47" t="n">
-        <v>6812449</v>
+        <v>6812544</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,7 +5367,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302667</v>
+        <v>122302656</v>
       </c>
       <c r="B48" t="n">
         <v>78645</v>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455438</v>
+        <v>455229</v>
       </c>
       <c r="R48" t="n">
-        <v>6812744</v>
+        <v>6812759</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122302603</v>
+        <v>122302737</v>
       </c>
       <c r="B49" t="n">
         <v>78645</v>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455413</v>
+        <v>455267</v>
       </c>
       <c r="R49" t="n">
-        <v>6812351</v>
+        <v>6812474</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -5571,10 +5571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122302579</v>
+        <v>122302670</v>
       </c>
       <c r="B50" t="n">
-        <v>78382</v>
+        <v>78645</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455212</v>
+        <v>455615</v>
       </c>
       <c r="R50" t="n">
-        <v>6812763</v>
+        <v>6812587</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,7 +5673,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302669</v>
+        <v>122302674</v>
       </c>
       <c r="B51" t="n">
         <v>78645</v>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455567</v>
+        <v>455758</v>
       </c>
       <c r="R51" t="n">
-        <v>6812725</v>
+        <v>6812559</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302594</v>
+        <v>122302669</v>
       </c>
       <c r="B52" t="n">
-        <v>78381</v>
+        <v>78645</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5791,21 +5791,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455177</v>
+        <v>455567</v>
       </c>
       <c r="R52" t="n">
-        <v>6812448</v>
+        <v>6812725</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302746</v>
+        <v>122302654</v>
       </c>
       <c r="B2" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455138</v>
+        <v>455187</v>
       </c>
       <c r="R2" t="n">
-        <v>6812473</v>
+        <v>6812780</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302538</v>
+        <v>122302671</v>
       </c>
       <c r="B3" t="n">
-        <v>79263</v>
+        <v>78646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455290</v>
+        <v>455616</v>
       </c>
       <c r="R3" t="n">
-        <v>6812727</v>
+        <v>6812570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302659</v>
+        <v>122302673</v>
       </c>
       <c r="B4" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455293</v>
+        <v>455747</v>
       </c>
       <c r="R4" t="n">
-        <v>6812728</v>
+        <v>6812550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302655</v>
+        <v>122302669</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455201</v>
+        <v>455567</v>
       </c>
       <c r="R5" t="n">
-        <v>6812767</v>
+        <v>6812725</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302671</v>
+        <v>122302579</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>78383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455616</v>
+        <v>455212</v>
       </c>
       <c r="R6" t="n">
-        <v>6812570</v>
+        <v>6812763</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302748</v>
+        <v>122302605</v>
       </c>
       <c r="B7" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455119</v>
+        <v>455043</v>
       </c>
       <c r="R7" t="n">
-        <v>6812489</v>
+        <v>6812499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302667</v>
+        <v>122302552</v>
       </c>
       <c r="B8" t="n">
-        <v>78645</v>
+        <v>78680</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455438</v>
+        <v>455409</v>
       </c>
       <c r="R8" t="n">
-        <v>6812744</v>
+        <v>6812375</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302579</v>
+        <v>122302668</v>
       </c>
       <c r="B9" t="n">
-        <v>78382</v>
+        <v>78646</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455212</v>
+        <v>455485</v>
       </c>
       <c r="R9" t="n">
-        <v>6812763</v>
+        <v>6812754</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302584</v>
+        <v>122302744</v>
       </c>
       <c r="B10" t="n">
-        <v>78382</v>
+        <v>78646</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1534,7 +1534,7 @@
         <v>455165</v>
       </c>
       <c r="R10" t="n">
-        <v>6812417</v>
+        <v>6812443</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302753</v>
+        <v>122302594</v>
       </c>
       <c r="B11" t="n">
-        <v>78645</v>
+        <v>78382</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454977</v>
+        <v>455177</v>
       </c>
       <c r="R11" t="n">
-        <v>6812451</v>
+        <v>6812448</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302747</v>
+        <v>122302583</v>
       </c>
       <c r="B12" t="n">
-        <v>78645</v>
+        <v>78383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455137</v>
+        <v>455177</v>
       </c>
       <c r="R12" t="n">
-        <v>6812474</v>
+        <v>6812448</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302650</v>
+        <v>122302745</v>
       </c>
       <c r="B13" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455089</v>
+        <v>455154</v>
       </c>
       <c r="R13" t="n">
-        <v>6812828</v>
+        <v>6812449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302604</v>
+        <v>122302753</v>
       </c>
       <c r="B14" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455405</v>
+        <v>454977</v>
       </c>
       <c r="R14" t="n">
-        <v>6812359</v>
+        <v>6812451</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302725</v>
+        <v>122302747</v>
       </c>
       <c r="B15" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455413</v>
+        <v>455137</v>
       </c>
       <c r="R15" t="n">
-        <v>6812371</v>
+        <v>6812474</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302749</v>
+        <v>122302665</v>
       </c>
       <c r="B16" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455098</v>
+        <v>455420</v>
       </c>
       <c r="R16" t="n">
-        <v>6812474</v>
+        <v>6812744</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302727</v>
+        <v>122302743</v>
       </c>
       <c r="B17" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455408</v>
+        <v>455165</v>
       </c>
       <c r="R17" t="n">
-        <v>6812407</v>
+        <v>6812417</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302751</v>
+        <v>122302650</v>
       </c>
       <c r="B18" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454998</v>
+        <v>455089</v>
       </c>
       <c r="R18" t="n">
-        <v>6812459</v>
+        <v>6812828</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302750</v>
+        <v>122302585</v>
       </c>
       <c r="B19" t="n">
-        <v>78645</v>
+        <v>78383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455083</v>
+        <v>454995</v>
       </c>
       <c r="R19" t="n">
-        <v>6812476</v>
+        <v>6812454</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2514,7 +2514,7 @@
         <v>122302736</v>
       </c>
       <c r="B20" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302658</v>
+        <v>122302537</v>
       </c>
       <c r="B21" t="n">
-        <v>78645</v>
+        <v>79264</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455259</v>
+        <v>455203</v>
       </c>
       <c r="R21" t="n">
-        <v>6812731</v>
+        <v>6812760</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302537</v>
+        <v>122302750</v>
       </c>
       <c r="B22" t="n">
-        <v>79263</v>
+        <v>78646</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455203</v>
+        <v>455083</v>
       </c>
       <c r="R22" t="n">
-        <v>6812760</v>
+        <v>6812476</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302668</v>
+        <v>122302672</v>
       </c>
       <c r="B23" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455485</v>
+        <v>455638</v>
       </c>
       <c r="R23" t="n">
-        <v>6812754</v>
+        <v>6812544</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302553</v>
+        <v>122302652</v>
       </c>
       <c r="B24" t="n">
-        <v>79234</v>
+        <v>78646</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455736</v>
+        <v>455165</v>
       </c>
       <c r="R24" t="n">
-        <v>6812556</v>
+        <v>6812792</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302726</v>
+        <v>122302656</v>
       </c>
       <c r="B25" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455407</v>
+        <v>455229</v>
       </c>
       <c r="R25" t="n">
-        <v>6812392</v>
+        <v>6812759</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302654</v>
+        <v>122302670</v>
       </c>
       <c r="B26" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455187</v>
+        <v>455615</v>
       </c>
       <c r="R26" t="n">
-        <v>6812780</v>
+        <v>6812587</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302673</v>
+        <v>122302749</v>
       </c>
       <c r="B27" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455747</v>
+        <v>455098</v>
       </c>
       <c r="R27" t="n">
-        <v>6812550</v>
+        <v>6812474</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302603</v>
+        <v>122302666</v>
       </c>
       <c r="B28" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455413</v>
+        <v>455428</v>
       </c>
       <c r="R28" t="n">
-        <v>6812351</v>
+        <v>6812747</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122302666</v>
+        <v>122302655</v>
       </c>
       <c r="B29" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455428</v>
+        <v>455201</v>
       </c>
       <c r="R29" t="n">
-        <v>6812747</v>
+        <v>6812767</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302773</v>
+        <v>122302538</v>
       </c>
       <c r="B30" t="n">
-        <v>78029</v>
+        <v>79264</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454992</v>
+        <v>455290</v>
       </c>
       <c r="R30" t="n">
-        <v>6812487</v>
+        <v>6812727</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302594</v>
+        <v>122302746</v>
       </c>
       <c r="B31" t="n">
-        <v>78381</v>
+        <v>78646</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455177</v>
+        <v>455138</v>
       </c>
       <c r="R31" t="n">
-        <v>6812448</v>
+        <v>6812473</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302585</v>
+        <v>122302727</v>
       </c>
       <c r="B32" t="n">
-        <v>78382</v>
+        <v>78646</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454995</v>
+        <v>455408</v>
       </c>
       <c r="R32" t="n">
-        <v>6812454</v>
+        <v>6812407</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122302743</v>
+        <v>122302659</v>
       </c>
       <c r="B33" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455165</v>
+        <v>455293</v>
       </c>
       <c r="R33" t="n">
-        <v>6812417</v>
+        <v>6812728</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122302552</v>
+        <v>122302603</v>
       </c>
       <c r="B34" t="n">
-        <v>78679</v>
+        <v>78646</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455409</v>
+        <v>455413</v>
       </c>
       <c r="R34" t="n">
-        <v>6812375</v>
+        <v>6812351</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122302744</v>
+        <v>122302752</v>
       </c>
       <c r="B35" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455165</v>
+        <v>454985</v>
       </c>
       <c r="R35" t="n">
-        <v>6812443</v>
+        <v>6812455</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122302651</v>
+        <v>122302737</v>
       </c>
       <c r="B36" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455119</v>
+        <v>455267</v>
       </c>
       <c r="R36" t="n">
-        <v>6812817</v>
+        <v>6812474</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302605</v>
+        <v>122302751</v>
       </c>
       <c r="B37" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455043</v>
+        <v>454998</v>
       </c>
       <c r="R37" t="n">
-        <v>6812499</v>
+        <v>6812459</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302724</v>
+        <v>122302754</v>
       </c>
       <c r="B38" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455449</v>
+        <v>454970</v>
       </c>
       <c r="R38" t="n">
-        <v>6812352</v>
+        <v>6812456</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302657</v>
+        <v>122302553</v>
       </c>
       <c r="B39" t="n">
-        <v>78645</v>
+        <v>79235</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455243</v>
+        <v>455736</v>
       </c>
       <c r="R39" t="n">
-        <v>6812747</v>
+        <v>6812556</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122302752</v>
+        <v>122302653</v>
       </c>
       <c r="B40" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454985</v>
+        <v>455173</v>
       </c>
       <c r="R40" t="n">
-        <v>6812455</v>
+        <v>6812786</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302665</v>
+        <v>122302667</v>
       </c>
       <c r="B41" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455420</v>
+        <v>455438</v>
       </c>
       <c r="R41" t="n">
         <v>6812744</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302745</v>
+        <v>122302726</v>
       </c>
       <c r="B42" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455154</v>
+        <v>455407</v>
       </c>
       <c r="R42" t="n">
-        <v>6812449</v>
+        <v>6812392</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -4857,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302754</v>
+        <v>122302658</v>
       </c>
       <c r="B43" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454970</v>
+        <v>455259</v>
       </c>
       <c r="R43" t="n">
-        <v>6812456</v>
+        <v>6812731</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302653</v>
+        <v>122302748</v>
       </c>
       <c r="B44" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455173</v>
+        <v>455119</v>
       </c>
       <c r="R44" t="n">
-        <v>6812786</v>
+        <v>6812489</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302652</v>
+        <v>122302725</v>
       </c>
       <c r="B45" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455165</v>
+        <v>455413</v>
       </c>
       <c r="R45" t="n">
-        <v>6812792</v>
+        <v>6812371</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5163,10 +5163,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122302583</v>
+        <v>122302773</v>
       </c>
       <c r="B46" t="n">
-        <v>78382</v>
+        <v>78030</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5179,21 +5179,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455177</v>
+        <v>454992</v>
       </c>
       <c r="R46" t="n">
-        <v>6812448</v>
+        <v>6812487</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122302672</v>
+        <v>122302724</v>
       </c>
       <c r="B47" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455638</v>
+        <v>455449</v>
       </c>
       <c r="R47" t="n">
-        <v>6812544</v>
+        <v>6812352</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5367,10 +5367,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302656</v>
+        <v>122302674</v>
       </c>
       <c r="B48" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455229</v>
+        <v>455758</v>
       </c>
       <c r="R48" t="n">
-        <v>6812759</v>
+        <v>6812559</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5469,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122302737</v>
+        <v>122302584</v>
       </c>
       <c r="B49" t="n">
-        <v>78645</v>
+        <v>78383</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5485,21 +5485,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455267</v>
+        <v>455165</v>
       </c>
       <c r="R49" t="n">
-        <v>6812474</v>
+        <v>6812417</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,10 +5571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122302670</v>
+        <v>122302651</v>
       </c>
       <c r="B50" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455615</v>
+        <v>455119</v>
       </c>
       <c r="R50" t="n">
-        <v>6812587</v>
+        <v>6812817</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302674</v>
+        <v>122302604</v>
       </c>
       <c r="B51" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455758</v>
+        <v>455405</v>
       </c>
       <c r="R51" t="n">
-        <v>6812559</v>
+        <v>6812359</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -5775,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302669</v>
+        <v>122302657</v>
       </c>
       <c r="B52" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455567</v>
+        <v>455243</v>
       </c>
       <c r="R52" t="n">
-        <v>6812725</v>
+        <v>6812747</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302654</v>
+        <v>122302553</v>
       </c>
       <c r="B2" t="n">
-        <v>78646</v>
+        <v>79235</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455187</v>
+        <v>455736</v>
       </c>
       <c r="R2" t="n">
-        <v>6812780</v>
+        <v>6812556</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302671</v>
+        <v>122302665</v>
       </c>
       <c r="B3" t="n">
         <v>78646</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455616</v>
+        <v>455420</v>
       </c>
       <c r="R3" t="n">
-        <v>6812570</v>
+        <v>6812744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302673</v>
+        <v>122302725</v>
       </c>
       <c r="B4" t="n">
         <v>78646</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455747</v>
+        <v>455413</v>
       </c>
       <c r="R4" t="n">
-        <v>6812550</v>
+        <v>6812371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302669</v>
+        <v>122302737</v>
       </c>
       <c r="B5" t="n">
         <v>78646</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455567</v>
+        <v>455267</v>
       </c>
       <c r="R5" t="n">
-        <v>6812725</v>
+        <v>6812474</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302579</v>
+        <v>122302668</v>
       </c>
       <c r="B6" t="n">
-        <v>78383</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455212</v>
+        <v>455485</v>
       </c>
       <c r="R6" t="n">
-        <v>6812763</v>
+        <v>6812754</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302605</v>
+        <v>122302745</v>
       </c>
       <c r="B7" t="n">
         <v>78646</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455043</v>
+        <v>455154</v>
       </c>
       <c r="R7" t="n">
-        <v>6812499</v>
+        <v>6812449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302552</v>
+        <v>122302605</v>
       </c>
       <c r="B8" t="n">
-        <v>78680</v>
+        <v>78646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455409</v>
+        <v>455043</v>
       </c>
       <c r="R8" t="n">
-        <v>6812375</v>
+        <v>6812499</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302668</v>
+        <v>122302670</v>
       </c>
       <c r="B9" t="n">
         <v>78646</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455485</v>
+        <v>455615</v>
       </c>
       <c r="R9" t="n">
-        <v>6812754</v>
+        <v>6812587</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302744</v>
+        <v>122302671</v>
       </c>
       <c r="B10" t="n">
         <v>78646</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455165</v>
+        <v>455616</v>
       </c>
       <c r="R10" t="n">
-        <v>6812443</v>
+        <v>6812570</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302594</v>
+        <v>122302585</v>
       </c>
       <c r="B11" t="n">
-        <v>78382</v>
+        <v>78383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455177</v>
+        <v>454995</v>
       </c>
       <c r="R11" t="n">
-        <v>6812448</v>
+        <v>6812454</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302583</v>
+        <v>122302744</v>
       </c>
       <c r="B12" t="n">
-        <v>78383</v>
+        <v>78646</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455177</v>
+        <v>455165</v>
       </c>
       <c r="R12" t="n">
-        <v>6812448</v>
+        <v>6812443</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302745</v>
+        <v>122302603</v>
       </c>
       <c r="B13" t="n">
         <v>78646</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455154</v>
+        <v>455413</v>
       </c>
       <c r="R13" t="n">
-        <v>6812449</v>
+        <v>6812351</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302753</v>
+        <v>122302747</v>
       </c>
       <c r="B14" t="n">
         <v>78646</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454977</v>
+        <v>455137</v>
       </c>
       <c r="R14" t="n">
-        <v>6812451</v>
+        <v>6812474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302747</v>
+        <v>122302674</v>
       </c>
       <c r="B15" t="n">
         <v>78646</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455137</v>
+        <v>455758</v>
       </c>
       <c r="R15" t="n">
-        <v>6812474</v>
+        <v>6812559</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302665</v>
+        <v>122302724</v>
       </c>
       <c r="B16" t="n">
         <v>78646</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455420</v>
+        <v>455449</v>
       </c>
       <c r="R16" t="n">
-        <v>6812744</v>
+        <v>6812352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302743</v>
+        <v>122302736</v>
       </c>
       <c r="B17" t="n">
         <v>78646</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455165</v>
+        <v>455295</v>
       </c>
       <c r="R17" t="n">
-        <v>6812417</v>
+        <v>6812491</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302650</v>
+        <v>122302753</v>
       </c>
       <c r="B18" t="n">
         <v>78646</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455089</v>
+        <v>454977</v>
       </c>
       <c r="R18" t="n">
-        <v>6812828</v>
+        <v>6812451</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302585</v>
+        <v>122302751</v>
       </c>
       <c r="B19" t="n">
-        <v>78383</v>
+        <v>78646</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454995</v>
+        <v>454998</v>
       </c>
       <c r="R19" t="n">
-        <v>6812454</v>
+        <v>6812459</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302736</v>
+        <v>122302584</v>
       </c>
       <c r="B20" t="n">
-        <v>78646</v>
+        <v>78383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455295</v>
+        <v>455165</v>
       </c>
       <c r="R20" t="n">
-        <v>6812491</v>
+        <v>6812417</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302537</v>
+        <v>122302673</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>78646</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455203</v>
+        <v>455747</v>
       </c>
       <c r="R21" t="n">
-        <v>6812760</v>
+        <v>6812550</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302672</v>
+        <v>122302652</v>
       </c>
       <c r="B23" t="n">
         <v>78646</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455638</v>
+        <v>455165</v>
       </c>
       <c r="R23" t="n">
-        <v>6812544</v>
+        <v>6812792</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302652</v>
+        <v>122302658</v>
       </c>
       <c r="B24" t="n">
         <v>78646</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455165</v>
+        <v>455259</v>
       </c>
       <c r="R24" t="n">
-        <v>6812792</v>
+        <v>6812731</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302656</v>
+        <v>122302748</v>
       </c>
       <c r="B25" t="n">
         <v>78646</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455229</v>
+        <v>455119</v>
       </c>
       <c r="R25" t="n">
-        <v>6812759</v>
+        <v>6812489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302670</v>
+        <v>122302667</v>
       </c>
       <c r="B26" t="n">
         <v>78646</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455615</v>
+        <v>455438</v>
       </c>
       <c r="R26" t="n">
-        <v>6812587</v>
+        <v>6812744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,7 +3225,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302749</v>
+        <v>122302743</v>
       </c>
       <c r="B27" t="n">
         <v>78646</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455098</v>
+        <v>455165</v>
       </c>
       <c r="R27" t="n">
-        <v>6812474</v>
+        <v>6812417</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302666</v>
+        <v>122302657</v>
       </c>
       <c r="B28" t="n">
         <v>78646</v>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455428</v>
+        <v>455243</v>
       </c>
       <c r="R28" t="n">
         <v>6812747</v>
@@ -3429,7 +3429,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122302655</v>
+        <v>122302653</v>
       </c>
       <c r="B29" t="n">
         <v>78646</v>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455201</v>
+        <v>455173</v>
       </c>
       <c r="R29" t="n">
-        <v>6812767</v>
+        <v>6812786</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302538</v>
+        <v>122302752</v>
       </c>
       <c r="B30" t="n">
-        <v>79264</v>
+        <v>78646</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455290</v>
+        <v>454985</v>
       </c>
       <c r="R30" t="n">
-        <v>6812727</v>
+        <v>6812455</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,7 +3633,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302746</v>
+        <v>122302672</v>
       </c>
       <c r="B31" t="n">
         <v>78646</v>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455138</v>
+        <v>455638</v>
       </c>
       <c r="R31" t="n">
-        <v>6812473</v>
+        <v>6812544</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302727</v>
+        <v>122302754</v>
       </c>
       <c r="B32" t="n">
         <v>78646</v>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455408</v>
+        <v>454970</v>
       </c>
       <c r="R32" t="n">
-        <v>6812407</v>
+        <v>6812456</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122302659</v>
+        <v>122302537</v>
       </c>
       <c r="B33" t="n">
-        <v>78646</v>
+        <v>79264</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455293</v>
+        <v>455203</v>
       </c>
       <c r="R33" t="n">
-        <v>6812728</v>
+        <v>6812760</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122302603</v>
+        <v>122302773</v>
       </c>
       <c r="B34" t="n">
-        <v>78646</v>
+        <v>78030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455413</v>
+        <v>454992</v>
       </c>
       <c r="R34" t="n">
-        <v>6812351</v>
+        <v>6812487</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122302752</v>
+        <v>122302650</v>
       </c>
       <c r="B35" t="n">
         <v>78646</v>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454985</v>
+        <v>455089</v>
       </c>
       <c r="R35" t="n">
-        <v>6812455</v>
+        <v>6812828</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122302737</v>
+        <v>122302746</v>
       </c>
       <c r="B36" t="n">
         <v>78646</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455267</v>
+        <v>455138</v>
       </c>
       <c r="R36" t="n">
-        <v>6812474</v>
+        <v>6812473</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302751</v>
+        <v>122302594</v>
       </c>
       <c r="B37" t="n">
-        <v>78646</v>
+        <v>78382</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4261,21 +4261,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454998</v>
+        <v>455177</v>
       </c>
       <c r="R37" t="n">
-        <v>6812459</v>
+        <v>6812448</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302754</v>
+        <v>122302583</v>
       </c>
       <c r="B38" t="n">
-        <v>78646</v>
+        <v>78383</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454970</v>
+        <v>455177</v>
       </c>
       <c r="R38" t="n">
-        <v>6812456</v>
+        <v>6812448</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302553</v>
+        <v>122302538</v>
       </c>
       <c r="B39" t="n">
-        <v>79235</v>
+        <v>79264</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455736</v>
+        <v>455290</v>
       </c>
       <c r="R39" t="n">
-        <v>6812556</v>
+        <v>6812727</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122302653</v>
+        <v>122302579</v>
       </c>
       <c r="B40" t="n">
-        <v>78646</v>
+        <v>78383</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455173</v>
+        <v>455212</v>
       </c>
       <c r="R40" t="n">
-        <v>6812786</v>
+        <v>6812763</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302667</v>
+        <v>122302552</v>
       </c>
       <c r="B41" t="n">
-        <v>78646</v>
+        <v>78680</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455438</v>
+        <v>455409</v>
       </c>
       <c r="R41" t="n">
-        <v>6812744</v>
+        <v>6812375</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4755,7 +4755,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302726</v>
+        <v>122302656</v>
       </c>
       <c r="B42" t="n">
         <v>78646</v>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455407</v>
+        <v>455229</v>
       </c>
       <c r="R42" t="n">
-        <v>6812392</v>
+        <v>6812759</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -4857,7 +4857,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302658</v>
+        <v>122302727</v>
       </c>
       <c r="B43" t="n">
         <v>78646</v>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455259</v>
+        <v>455408</v>
       </c>
       <c r="R43" t="n">
-        <v>6812731</v>
+        <v>6812407</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -4959,7 +4959,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302748</v>
+        <v>122302669</v>
       </c>
       <c r="B44" t="n">
         <v>78646</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455119</v>
+        <v>455567</v>
       </c>
       <c r="R44" t="n">
-        <v>6812489</v>
+        <v>6812725</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,7 +5061,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302725</v>
+        <v>122302654</v>
       </c>
       <c r="B45" t="n">
         <v>78646</v>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455413</v>
+        <v>455187</v>
       </c>
       <c r="R45" t="n">
-        <v>6812371</v>
+        <v>6812780</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5163,10 +5163,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122302773</v>
+        <v>122302726</v>
       </c>
       <c r="B46" t="n">
-        <v>78030</v>
+        <v>78646</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5179,21 +5179,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>454992</v>
+        <v>455407</v>
       </c>
       <c r="R46" t="n">
-        <v>6812487</v>
+        <v>6812392</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5265,7 +5265,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122302724</v>
+        <v>122302655</v>
       </c>
       <c r="B47" t="n">
         <v>78646</v>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455449</v>
+        <v>455201</v>
       </c>
       <c r="R47" t="n">
-        <v>6812352</v>
+        <v>6812767</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -5367,7 +5367,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302674</v>
+        <v>122302651</v>
       </c>
       <c r="B48" t="n">
         <v>78646</v>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455758</v>
+        <v>455119</v>
       </c>
       <c r="R48" t="n">
-        <v>6812559</v>
+        <v>6812817</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5469,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122302584</v>
+        <v>122302749</v>
       </c>
       <c r="B49" t="n">
-        <v>78383</v>
+        <v>78646</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5485,21 +5485,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455165</v>
+        <v>455098</v>
       </c>
       <c r="R49" t="n">
-        <v>6812417</v>
+        <v>6812474</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,7 +5571,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122302651</v>
+        <v>122302666</v>
       </c>
       <c r="B50" t="n">
         <v>78646</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455119</v>
+        <v>455428</v>
       </c>
       <c r="R50" t="n">
-        <v>6812817</v>
+        <v>6812747</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,7 +5673,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302604</v>
+        <v>122302659</v>
       </c>
       <c r="B51" t="n">
         <v>78646</v>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455405</v>
+        <v>455293</v>
       </c>
       <c r="R51" t="n">
-        <v>6812359</v>
+        <v>6812728</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -5775,7 +5775,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302657</v>
+        <v>122302604</v>
       </c>
       <c r="B52" t="n">
         <v>78646</v>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455243</v>
+        <v>455405</v>
       </c>
       <c r="R52" t="n">
-        <v>6812747</v>
+        <v>6812359</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302553</v>
+        <v>122302658</v>
       </c>
       <c r="B2" t="n">
-        <v>79235</v>
+        <v>78651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455736</v>
+        <v>455259</v>
       </c>
       <c r="R2" t="n">
-        <v>6812556</v>
+        <v>6812731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302665</v>
+        <v>122302651</v>
       </c>
       <c r="B3" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455420</v>
+        <v>455119</v>
       </c>
       <c r="R3" t="n">
-        <v>6812744</v>
+        <v>6812817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302725</v>
+        <v>122302553</v>
       </c>
       <c r="B4" t="n">
-        <v>78646</v>
+        <v>79240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455413</v>
+        <v>455736</v>
       </c>
       <c r="R4" t="n">
-        <v>6812371</v>
+        <v>6812556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302737</v>
+        <v>122302605</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455267</v>
+        <v>455043</v>
       </c>
       <c r="R5" t="n">
-        <v>6812474</v>
+        <v>6812499</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302668</v>
+        <v>122302659</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455485</v>
+        <v>455293</v>
       </c>
       <c r="R6" t="n">
-        <v>6812754</v>
+        <v>6812728</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302745</v>
+        <v>122302749</v>
       </c>
       <c r="B7" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455154</v>
+        <v>455098</v>
       </c>
       <c r="R7" t="n">
-        <v>6812449</v>
+        <v>6812474</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302605</v>
+        <v>122302552</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>78685</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455043</v>
+        <v>455409</v>
       </c>
       <c r="R8" t="n">
-        <v>6812499</v>
+        <v>6812375</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302670</v>
+        <v>122302752</v>
       </c>
       <c r="B9" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455615</v>
+        <v>454985</v>
       </c>
       <c r="R9" t="n">
-        <v>6812587</v>
+        <v>6812455</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302671</v>
+        <v>122302655</v>
       </c>
       <c r="B10" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455616</v>
+        <v>455201</v>
       </c>
       <c r="R10" t="n">
-        <v>6812570</v>
+        <v>6812767</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302585</v>
+        <v>122302727</v>
       </c>
       <c r="B11" t="n">
-        <v>78383</v>
+        <v>78651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454995</v>
+        <v>455408</v>
       </c>
       <c r="R11" t="n">
-        <v>6812454</v>
+        <v>6812407</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302744</v>
+        <v>122302652</v>
       </c>
       <c r="B12" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>455165</v>
       </c>
       <c r="R12" t="n">
-        <v>6812443</v>
+        <v>6812792</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302603</v>
+        <v>122302773</v>
       </c>
       <c r="B13" t="n">
-        <v>78646</v>
+        <v>78035</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455413</v>
+        <v>454992</v>
       </c>
       <c r="R13" t="n">
-        <v>6812351</v>
+        <v>6812487</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302747</v>
+        <v>122302668</v>
       </c>
       <c r="B14" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455137</v>
+        <v>455485</v>
       </c>
       <c r="R14" t="n">
-        <v>6812474</v>
+        <v>6812754</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302674</v>
+        <v>122302603</v>
       </c>
       <c r="B15" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455758</v>
+        <v>455413</v>
       </c>
       <c r="R15" t="n">
-        <v>6812559</v>
+        <v>6812351</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302724</v>
+        <v>122302584</v>
       </c>
       <c r="B16" t="n">
-        <v>78646</v>
+        <v>78388</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455449</v>
+        <v>455165</v>
       </c>
       <c r="R16" t="n">
-        <v>6812352</v>
+        <v>6812417</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302736</v>
+        <v>122302653</v>
       </c>
       <c r="B17" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455295</v>
+        <v>455173</v>
       </c>
       <c r="R17" t="n">
-        <v>6812491</v>
+        <v>6812786</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302753</v>
+        <v>122302724</v>
       </c>
       <c r="B18" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454977</v>
+        <v>455449</v>
       </c>
       <c r="R18" t="n">
-        <v>6812451</v>
+        <v>6812352</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302751</v>
+        <v>122302673</v>
       </c>
       <c r="B19" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454998</v>
+        <v>455747</v>
       </c>
       <c r="R19" t="n">
-        <v>6812459</v>
+        <v>6812550</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302584</v>
+        <v>122302583</v>
       </c>
       <c r="B20" t="n">
-        <v>78383</v>
+        <v>78388</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455165</v>
+        <v>455177</v>
       </c>
       <c r="R20" t="n">
-        <v>6812417</v>
+        <v>6812448</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302673</v>
+        <v>122302753</v>
       </c>
       <c r="B21" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455747</v>
+        <v>454977</v>
       </c>
       <c r="R21" t="n">
-        <v>6812550</v>
+        <v>6812451</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302750</v>
+        <v>122302667</v>
       </c>
       <c r="B22" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455083</v>
+        <v>455438</v>
       </c>
       <c r="R22" t="n">
-        <v>6812476</v>
+        <v>6812744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302652</v>
+        <v>122302657</v>
       </c>
       <c r="B23" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455165</v>
+        <v>455243</v>
       </c>
       <c r="R23" t="n">
-        <v>6812792</v>
+        <v>6812747</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302658</v>
+        <v>122302537</v>
       </c>
       <c r="B24" t="n">
-        <v>78646</v>
+        <v>79269</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455259</v>
+        <v>455203</v>
       </c>
       <c r="R24" t="n">
-        <v>6812731</v>
+        <v>6812760</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302748</v>
+        <v>122302747</v>
       </c>
       <c r="B25" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455119</v>
+        <v>455137</v>
       </c>
       <c r="R25" t="n">
-        <v>6812489</v>
+        <v>6812474</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302667</v>
+        <v>122302754</v>
       </c>
       <c r="B26" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455438</v>
+        <v>454970</v>
       </c>
       <c r="R26" t="n">
-        <v>6812744</v>
+        <v>6812456</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302743</v>
+        <v>122302674</v>
       </c>
       <c r="B27" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455165</v>
+        <v>455758</v>
       </c>
       <c r="R27" t="n">
-        <v>6812417</v>
+        <v>6812559</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302657</v>
+        <v>122302725</v>
       </c>
       <c r="B28" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455243</v>
+        <v>455413</v>
       </c>
       <c r="R28" t="n">
-        <v>6812747</v>
+        <v>6812371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122302653</v>
+        <v>122302746</v>
       </c>
       <c r="B29" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455173</v>
+        <v>455138</v>
       </c>
       <c r="R29" t="n">
-        <v>6812786</v>
+        <v>6812473</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302752</v>
+        <v>122302726</v>
       </c>
       <c r="B30" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454985</v>
+        <v>455407</v>
       </c>
       <c r="R30" t="n">
-        <v>6812455</v>
+        <v>6812392</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302672</v>
+        <v>122302748</v>
       </c>
       <c r="B31" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455638</v>
+        <v>455119</v>
       </c>
       <c r="R31" t="n">
-        <v>6812544</v>
+        <v>6812489</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302754</v>
+        <v>122302579</v>
       </c>
       <c r="B32" t="n">
-        <v>78646</v>
+        <v>78388</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454970</v>
+        <v>455212</v>
       </c>
       <c r="R32" t="n">
-        <v>6812456</v>
+        <v>6812763</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122302537</v>
+        <v>122302604</v>
       </c>
       <c r="B33" t="n">
-        <v>79264</v>
+        <v>78651</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455203</v>
+        <v>455405</v>
       </c>
       <c r="R33" t="n">
-        <v>6812760</v>
+        <v>6812359</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122302773</v>
+        <v>122302656</v>
       </c>
       <c r="B34" t="n">
-        <v>78030</v>
+        <v>78651</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454992</v>
+        <v>455229</v>
       </c>
       <c r="R34" t="n">
-        <v>6812487</v>
+        <v>6812759</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122302650</v>
+        <v>122302594</v>
       </c>
       <c r="B35" t="n">
-        <v>78646</v>
+        <v>78387</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4057,21 +4057,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455089</v>
+        <v>455177</v>
       </c>
       <c r="R35" t="n">
-        <v>6812828</v>
+        <v>6812448</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122302746</v>
+        <v>122302737</v>
       </c>
       <c r="B36" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455138</v>
+        <v>455267</v>
       </c>
       <c r="R36" t="n">
-        <v>6812473</v>
+        <v>6812474</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302594</v>
+        <v>122302672</v>
       </c>
       <c r="B37" t="n">
-        <v>78382</v>
+        <v>78651</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4261,21 +4261,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455177</v>
+        <v>455638</v>
       </c>
       <c r="R37" t="n">
-        <v>6812448</v>
+        <v>6812544</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302583</v>
+        <v>122302736</v>
       </c>
       <c r="B38" t="n">
-        <v>78383</v>
+        <v>78651</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455177</v>
+        <v>455295</v>
       </c>
       <c r="R38" t="n">
-        <v>6812448</v>
+        <v>6812491</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302538</v>
+        <v>122302745</v>
       </c>
       <c r="B39" t="n">
-        <v>79264</v>
+        <v>78651</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455290</v>
+        <v>455154</v>
       </c>
       <c r="R39" t="n">
-        <v>6812727</v>
+        <v>6812449</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122302579</v>
+        <v>122302743</v>
       </c>
       <c r="B40" t="n">
-        <v>78383</v>
+        <v>78651</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455212</v>
+        <v>455165</v>
       </c>
       <c r="R40" t="n">
-        <v>6812763</v>
+        <v>6812417</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302552</v>
+        <v>122302744</v>
       </c>
       <c r="B41" t="n">
-        <v>78680</v>
+        <v>78651</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455409</v>
+        <v>455165</v>
       </c>
       <c r="R41" t="n">
-        <v>6812375</v>
+        <v>6812443</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302656</v>
+        <v>122302670</v>
       </c>
       <c r="B42" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455229</v>
+        <v>455615</v>
       </c>
       <c r="R42" t="n">
-        <v>6812759</v>
+        <v>6812587</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302727</v>
+        <v>122302666</v>
       </c>
       <c r="B43" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455408</v>
+        <v>455428</v>
       </c>
       <c r="R43" t="n">
-        <v>6812407</v>
+        <v>6812747</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302669</v>
+        <v>122302654</v>
       </c>
       <c r="B44" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455567</v>
+        <v>455187</v>
       </c>
       <c r="R44" t="n">
-        <v>6812725</v>
+        <v>6812780</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302654</v>
+        <v>122302665</v>
       </c>
       <c r="B45" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455187</v>
+        <v>455420</v>
       </c>
       <c r="R45" t="n">
-        <v>6812780</v>
+        <v>6812744</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122302726</v>
+        <v>122302750</v>
       </c>
       <c r="B46" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455407</v>
+        <v>455083</v>
       </c>
       <c r="R46" t="n">
-        <v>6812392</v>
+        <v>6812476</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5265,10 +5265,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122302655</v>
+        <v>122302669</v>
       </c>
       <c r="B47" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455201</v>
+        <v>455567</v>
       </c>
       <c r="R47" t="n">
-        <v>6812767</v>
+        <v>6812725</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,10 +5367,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302651</v>
+        <v>122302671</v>
       </c>
       <c r="B48" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455119</v>
+        <v>455616</v>
       </c>
       <c r="R48" t="n">
-        <v>6812817</v>
+        <v>6812570</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5469,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122302749</v>
+        <v>122302650</v>
       </c>
       <c r="B49" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455098</v>
+        <v>455089</v>
       </c>
       <c r="R49" t="n">
-        <v>6812474</v>
+        <v>6812828</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,10 +5571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122302666</v>
+        <v>122302585</v>
       </c>
       <c r="B50" t="n">
-        <v>78646</v>
+        <v>78388</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455428</v>
+        <v>454995</v>
       </c>
       <c r="R50" t="n">
-        <v>6812747</v>
+        <v>6812454</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302659</v>
+        <v>122302538</v>
       </c>
       <c r="B51" t="n">
-        <v>78646</v>
+        <v>79269</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5689,21 +5689,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455293</v>
+        <v>455290</v>
       </c>
       <c r="R51" t="n">
-        <v>6812728</v>
+        <v>6812727</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302604</v>
+        <v>122302751</v>
       </c>
       <c r="B52" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455405</v>
+        <v>454998</v>
       </c>
       <c r="R52" t="n">
-        <v>6812359</v>
+        <v>6812459</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302658</v>
+        <v>122302751</v>
       </c>
       <c r="B2" t="n">
         <v>78651</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455259</v>
+        <v>454998</v>
       </c>
       <c r="R2" t="n">
-        <v>6812731</v>
+        <v>6812459</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302651</v>
+        <v>122302584</v>
       </c>
       <c r="B3" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455119</v>
+        <v>455165</v>
       </c>
       <c r="R3" t="n">
-        <v>6812817</v>
+        <v>6812417</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302553</v>
+        <v>122302746</v>
       </c>
       <c r="B4" t="n">
-        <v>79240</v>
+        <v>78651</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455736</v>
+        <v>455138</v>
       </c>
       <c r="R4" t="n">
-        <v>6812556</v>
+        <v>6812473</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302605</v>
+        <v>122302665</v>
       </c>
       <c r="B5" t="n">
         <v>78651</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455043</v>
+        <v>455420</v>
       </c>
       <c r="R5" t="n">
-        <v>6812499</v>
+        <v>6812744</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302659</v>
+        <v>122302655</v>
       </c>
       <c r="B6" t="n">
         <v>78651</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455293</v>
+        <v>455201</v>
       </c>
       <c r="R6" t="n">
-        <v>6812728</v>
+        <v>6812767</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302749</v>
+        <v>122302604</v>
       </c>
       <c r="B7" t="n">
         <v>78651</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455098</v>
+        <v>455405</v>
       </c>
       <c r="R7" t="n">
-        <v>6812474</v>
+        <v>6812359</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302552</v>
+        <v>122302583</v>
       </c>
       <c r="B8" t="n">
-        <v>78685</v>
+        <v>78388</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455409</v>
+        <v>455177</v>
       </c>
       <c r="R8" t="n">
-        <v>6812375</v>
+        <v>6812448</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302655</v>
+        <v>122302658</v>
       </c>
       <c r="B10" t="n">
         <v>78651</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455201</v>
+        <v>455259</v>
       </c>
       <c r="R10" t="n">
-        <v>6812767</v>
+        <v>6812731</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302727</v>
+        <v>122302747</v>
       </c>
       <c r="B11" t="n">
         <v>78651</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455408</v>
+        <v>455137</v>
       </c>
       <c r="R11" t="n">
-        <v>6812407</v>
+        <v>6812474</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302652</v>
+        <v>122302668</v>
       </c>
       <c r="B12" t="n">
         <v>78651</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455165</v>
+        <v>455485</v>
       </c>
       <c r="R12" t="n">
-        <v>6812792</v>
+        <v>6812754</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302773</v>
+        <v>122302727</v>
       </c>
       <c r="B13" t="n">
-        <v>78035</v>
+        <v>78651</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454992</v>
+        <v>455408</v>
       </c>
       <c r="R13" t="n">
-        <v>6812487</v>
+        <v>6812407</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302668</v>
+        <v>122302674</v>
       </c>
       <c r="B14" t="n">
         <v>78651</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455485</v>
+        <v>455758</v>
       </c>
       <c r="R14" t="n">
-        <v>6812754</v>
+        <v>6812559</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302603</v>
+        <v>122302726</v>
       </c>
       <c r="B15" t="n">
         <v>78651</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455413</v>
+        <v>455407</v>
       </c>
       <c r="R15" t="n">
-        <v>6812351</v>
+        <v>6812392</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302584</v>
+        <v>122302745</v>
       </c>
       <c r="B16" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455165</v>
+        <v>455154</v>
       </c>
       <c r="R16" t="n">
-        <v>6812417</v>
+        <v>6812449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302653</v>
+        <v>122302594</v>
       </c>
       <c r="B17" t="n">
-        <v>78651</v>
+        <v>78387</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455173</v>
+        <v>455177</v>
       </c>
       <c r="R17" t="n">
-        <v>6812786</v>
+        <v>6812448</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302724</v>
+        <v>122302749</v>
       </c>
       <c r="B18" t="n">
         <v>78651</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455449</v>
+        <v>455098</v>
       </c>
       <c r="R18" t="n">
-        <v>6812352</v>
+        <v>6812474</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302673</v>
+        <v>122302737</v>
       </c>
       <c r="B19" t="n">
         <v>78651</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455747</v>
+        <v>455267</v>
       </c>
       <c r="R19" t="n">
-        <v>6812550</v>
+        <v>6812474</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302583</v>
+        <v>122302651</v>
       </c>
       <c r="B20" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455177</v>
+        <v>455119</v>
       </c>
       <c r="R20" t="n">
-        <v>6812448</v>
+        <v>6812817</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302753</v>
+        <v>122302605</v>
       </c>
       <c r="B21" t="n">
         <v>78651</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454977</v>
+        <v>455043</v>
       </c>
       <c r="R21" t="n">
-        <v>6812451</v>
+        <v>6812499</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302667</v>
+        <v>122302657</v>
       </c>
       <c r="B22" t="n">
         <v>78651</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455438</v>
+        <v>455243</v>
       </c>
       <c r="R22" t="n">
-        <v>6812744</v>
+        <v>6812747</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302657</v>
+        <v>122302552</v>
       </c>
       <c r="B23" t="n">
-        <v>78651</v>
+        <v>78685</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455243</v>
+        <v>455409</v>
       </c>
       <c r="R23" t="n">
-        <v>6812747</v>
+        <v>6812375</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302537</v>
+        <v>122302671</v>
       </c>
       <c r="B24" t="n">
-        <v>79269</v>
+        <v>78651</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455203</v>
+        <v>455616</v>
       </c>
       <c r="R24" t="n">
-        <v>6812760</v>
+        <v>6812570</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302747</v>
+        <v>122302748</v>
       </c>
       <c r="B25" t="n">
         <v>78651</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455137</v>
+        <v>455119</v>
       </c>
       <c r="R25" t="n">
-        <v>6812474</v>
+        <v>6812489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302754</v>
+        <v>122302724</v>
       </c>
       <c r="B26" t="n">
         <v>78651</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454970</v>
+        <v>455449</v>
       </c>
       <c r="R26" t="n">
-        <v>6812456</v>
+        <v>6812352</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3225,7 +3225,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302674</v>
+        <v>122302656</v>
       </c>
       <c r="B27" t="n">
         <v>78651</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455758</v>
+        <v>455229</v>
       </c>
       <c r="R27" t="n">
-        <v>6812559</v>
+        <v>6812759</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302725</v>
+        <v>122302773</v>
       </c>
       <c r="B28" t="n">
-        <v>78651</v>
+        <v>78035</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455413</v>
+        <v>454992</v>
       </c>
       <c r="R28" t="n">
-        <v>6812371</v>
+        <v>6812487</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3429,7 +3429,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122302746</v>
+        <v>122302673</v>
       </c>
       <c r="B29" t="n">
         <v>78651</v>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455138</v>
+        <v>455747</v>
       </c>
       <c r="R29" t="n">
-        <v>6812473</v>
+        <v>6812550</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302726</v>
+        <v>122302725</v>
       </c>
       <c r="B30" t="n">
         <v>78651</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455407</v>
+        <v>455413</v>
       </c>
       <c r="R30" t="n">
-        <v>6812392</v>
+        <v>6812371</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,7 +3633,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302748</v>
+        <v>122302753</v>
       </c>
       <c r="B31" t="n">
         <v>78651</v>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455119</v>
+        <v>454977</v>
       </c>
       <c r="R31" t="n">
-        <v>6812489</v>
+        <v>6812451</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302579</v>
+        <v>122302653</v>
       </c>
       <c r="B32" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455212</v>
+        <v>455173</v>
       </c>
       <c r="R32" t="n">
-        <v>6812763</v>
+        <v>6812786</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122302604</v>
+        <v>122302538</v>
       </c>
       <c r="B33" t="n">
-        <v>78651</v>
+        <v>79269</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455405</v>
+        <v>455290</v>
       </c>
       <c r="R33" t="n">
-        <v>6812359</v>
+        <v>6812727</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3939,7 +3939,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122302656</v>
+        <v>122302750</v>
       </c>
       <c r="B34" t="n">
         <v>78651</v>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455229</v>
+        <v>455083</v>
       </c>
       <c r="R34" t="n">
-        <v>6812759</v>
+        <v>6812476</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122302594</v>
+        <v>122302672</v>
       </c>
       <c r="B35" t="n">
-        <v>78387</v>
+        <v>78651</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4057,21 +4057,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455177</v>
+        <v>455638</v>
       </c>
       <c r="R35" t="n">
-        <v>6812448</v>
+        <v>6812544</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122302737</v>
+        <v>122302659</v>
       </c>
       <c r="B36" t="n">
         <v>78651</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455267</v>
+        <v>455293</v>
       </c>
       <c r="R36" t="n">
-        <v>6812474</v>
+        <v>6812728</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302672</v>
+        <v>122302743</v>
       </c>
       <c r="B37" t="n">
         <v>78651</v>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455638</v>
+        <v>455165</v>
       </c>
       <c r="R37" t="n">
-        <v>6812544</v>
+        <v>6812417</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302736</v>
+        <v>122302754</v>
       </c>
       <c r="B38" t="n">
         <v>78651</v>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455295</v>
+        <v>454970</v>
       </c>
       <c r="R38" t="n">
-        <v>6812491</v>
+        <v>6812456</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302745</v>
+        <v>122302579</v>
       </c>
       <c r="B39" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455154</v>
+        <v>455212</v>
       </c>
       <c r="R39" t="n">
-        <v>6812449</v>
+        <v>6812763</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122302743</v>
+        <v>122302654</v>
       </c>
       <c r="B40" t="n">
         <v>78651</v>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455165</v>
+        <v>455187</v>
       </c>
       <c r="R40" t="n">
-        <v>6812417</v>
+        <v>6812780</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302744</v>
+        <v>122302585</v>
       </c>
       <c r="B41" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455165</v>
+        <v>454995</v>
       </c>
       <c r="R41" t="n">
-        <v>6812443</v>
+        <v>6812454</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302666</v>
+        <v>122302652</v>
       </c>
       <c r="B43" t="n">
         <v>78651</v>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455428</v>
+        <v>455165</v>
       </c>
       <c r="R43" t="n">
-        <v>6812747</v>
+        <v>6812792</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302654</v>
+        <v>122302667</v>
       </c>
       <c r="B44" t="n">
         <v>78651</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455187</v>
+        <v>455438</v>
       </c>
       <c r="R44" t="n">
-        <v>6812780</v>
+        <v>6812744</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302665</v>
+        <v>122302537</v>
       </c>
       <c r="B45" t="n">
-        <v>78651</v>
+        <v>79269</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,21 +5077,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455420</v>
+        <v>455203</v>
       </c>
       <c r="R45" t="n">
-        <v>6812744</v>
+        <v>6812760</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122302750</v>
+        <v>122302744</v>
       </c>
       <c r="B46" t="n">
         <v>78651</v>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455083</v>
+        <v>455165</v>
       </c>
       <c r="R46" t="n">
-        <v>6812476</v>
+        <v>6812443</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5367,10 +5367,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302671</v>
+        <v>122302553</v>
       </c>
       <c r="B48" t="n">
-        <v>78651</v>
+        <v>79240</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5383,21 +5383,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455616</v>
+        <v>455736</v>
       </c>
       <c r="R48" t="n">
-        <v>6812570</v>
+        <v>6812556</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122302650</v>
+        <v>122302736</v>
       </c>
       <c r="B49" t="n">
         <v>78651</v>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455089</v>
+        <v>455295</v>
       </c>
       <c r="R49" t="n">
-        <v>6812828</v>
+        <v>6812491</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,10 +5571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122302585</v>
+        <v>122302650</v>
       </c>
       <c r="B50" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>454995</v>
+        <v>455089</v>
       </c>
       <c r="R50" t="n">
-        <v>6812454</v>
+        <v>6812828</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302538</v>
+        <v>122302603</v>
       </c>
       <c r="B51" t="n">
-        <v>79269</v>
+        <v>78651</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5689,21 +5689,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455290</v>
+        <v>455413</v>
       </c>
       <c r="R51" t="n">
-        <v>6812727</v>
+        <v>6812351</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -5775,7 +5775,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302751</v>
+        <v>122302666</v>
       </c>
       <c r="B52" t="n">
         <v>78651</v>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>454998</v>
+        <v>455428</v>
       </c>
       <c r="R52" t="n">
-        <v>6812459</v>
+        <v>6812747</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302583</v>
+        <v>122302752</v>
       </c>
       <c r="B8" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455177</v>
+        <v>454985</v>
       </c>
       <c r="R8" t="n">
-        <v>6812448</v>
+        <v>6812455</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302752</v>
+        <v>122302658</v>
       </c>
       <c r="B9" t="n">
         <v>78651</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454985</v>
+        <v>455259</v>
       </c>
       <c r="R9" t="n">
-        <v>6812455</v>
+        <v>6812731</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302658</v>
+        <v>122302747</v>
       </c>
       <c r="B10" t="n">
         <v>78651</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455259</v>
+        <v>455137</v>
       </c>
       <c r="R10" t="n">
-        <v>6812731</v>
+        <v>6812474</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302747</v>
+        <v>122302583</v>
       </c>
       <c r="B11" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455137</v>
+        <v>455177</v>
       </c>
       <c r="R11" t="n">
-        <v>6812474</v>
+        <v>6812448</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302743</v>
+        <v>122302754</v>
       </c>
       <c r="B37" t="n">
         <v>78651</v>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455165</v>
+        <v>454970</v>
       </c>
       <c r="R37" t="n">
-        <v>6812417</v>
+        <v>6812456</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302754</v>
+        <v>122302743</v>
       </c>
       <c r="B38" t="n">
         <v>78651</v>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454970</v>
+        <v>455165</v>
       </c>
       <c r="R38" t="n">
-        <v>6812456</v>
+        <v>6812417</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302585</v>
+        <v>122302670</v>
       </c>
       <c r="B41" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454995</v>
+        <v>455615</v>
       </c>
       <c r="R41" t="n">
-        <v>6812454</v>
+        <v>6812587</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,7 +4755,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302670</v>
+        <v>122302652</v>
       </c>
       <c r="B42" t="n">
         <v>78651</v>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455615</v>
+        <v>455165</v>
       </c>
       <c r="R42" t="n">
-        <v>6812587</v>
+        <v>6812792</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302652</v>
+        <v>122302667</v>
       </c>
       <c r="B43" t="n">
         <v>78651</v>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455165</v>
+        <v>455438</v>
       </c>
       <c r="R43" t="n">
-        <v>6812792</v>
+        <v>6812744</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302667</v>
+        <v>122302585</v>
       </c>
       <c r="B44" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455438</v>
+        <v>454995</v>
       </c>
       <c r="R44" t="n">
-        <v>6812744</v>
+        <v>6812454</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302751</v>
+        <v>122302584</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454998</v>
+        <v>455165</v>
       </c>
       <c r="R2" t="n">
-        <v>6812459</v>
+        <v>6812417</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302584</v>
+        <v>122302751</v>
       </c>
       <c r="B3" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455165</v>
+        <v>454998</v>
       </c>
       <c r="R3" t="n">
-        <v>6812417</v>
+        <v>6812459</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302752</v>
+        <v>122302583</v>
       </c>
       <c r="B8" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454985</v>
+        <v>455177</v>
       </c>
       <c r="R8" t="n">
-        <v>6812455</v>
+        <v>6812448</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302658</v>
+        <v>122302752</v>
       </c>
       <c r="B9" t="n">
         <v>78651</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455259</v>
+        <v>454985</v>
       </c>
       <c r="R9" t="n">
-        <v>6812731</v>
+        <v>6812455</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302747</v>
+        <v>122302658</v>
       </c>
       <c r="B10" t="n">
         <v>78651</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455137</v>
+        <v>455259</v>
       </c>
       <c r="R10" t="n">
-        <v>6812474</v>
+        <v>6812731</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302583</v>
+        <v>122302747</v>
       </c>
       <c r="B11" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455177</v>
+        <v>455137</v>
       </c>
       <c r="R11" t="n">
-        <v>6812448</v>
+        <v>6812474</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302737</v>
+        <v>122302552</v>
       </c>
       <c r="B19" t="n">
-        <v>78651</v>
+        <v>78685</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455267</v>
+        <v>455409</v>
       </c>
       <c r="R19" t="n">
-        <v>6812474</v>
+        <v>6812375</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302651</v>
+        <v>122302737</v>
       </c>
       <c r="B20" t="n">
         <v>78651</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455119</v>
+        <v>455267</v>
       </c>
       <c r="R20" t="n">
-        <v>6812817</v>
+        <v>6812474</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302605</v>
+        <v>122302651</v>
       </c>
       <c r="B21" t="n">
         <v>78651</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455043</v>
+        <v>455119</v>
       </c>
       <c r="R21" t="n">
-        <v>6812499</v>
+        <v>6812817</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302657</v>
+        <v>122302605</v>
       </c>
       <c r="B22" t="n">
         <v>78651</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455243</v>
+        <v>455043</v>
       </c>
       <c r="R22" t="n">
-        <v>6812747</v>
+        <v>6812499</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302552</v>
+        <v>122302657</v>
       </c>
       <c r="B23" t="n">
-        <v>78685</v>
+        <v>78651</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455409</v>
+        <v>455243</v>
       </c>
       <c r="R23" t="n">
-        <v>6812375</v>
+        <v>6812747</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302670</v>
+        <v>122302585</v>
       </c>
       <c r="B41" t="n">
-        <v>78651</v>
+        <v>78388</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455615</v>
+        <v>454995</v>
       </c>
       <c r="R41" t="n">
-        <v>6812587</v>
+        <v>6812454</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,7 +4755,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302652</v>
+        <v>122302670</v>
       </c>
       <c r="B42" t="n">
         <v>78651</v>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455165</v>
+        <v>455615</v>
       </c>
       <c r="R42" t="n">
-        <v>6812792</v>
+        <v>6812587</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302667</v>
+        <v>122302652</v>
       </c>
       <c r="B43" t="n">
         <v>78651</v>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455438</v>
+        <v>455165</v>
       </c>
       <c r="R43" t="n">
-        <v>6812744</v>
+        <v>6812792</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302585</v>
+        <v>122302667</v>
       </c>
       <c r="B44" t="n">
-        <v>78388</v>
+        <v>78651</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454995</v>
+        <v>455438</v>
       </c>
       <c r="R44" t="n">
-        <v>6812454</v>
+        <v>6812744</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302584</v>
+        <v>122302604</v>
       </c>
       <c r="B2" t="n">
-        <v>78388</v>
+        <v>78652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455165</v>
+        <v>455405</v>
       </c>
       <c r="R2" t="n">
-        <v>6812417</v>
+        <v>6812359</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302751</v>
+        <v>122302657</v>
       </c>
       <c r="B3" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,11 +790,6 @@
       <c r="E3" t="n">
         <v>6425</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454998</v>
+        <v>455243</v>
       </c>
       <c r="R3" t="n">
-        <v>6812459</v>
+        <v>6812747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302746</v>
+        <v>122302652</v>
       </c>
       <c r="B4" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,11 +887,6 @@
       <c r="E4" t="n">
         <v>6425</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455138</v>
+        <v>455165</v>
       </c>
       <c r="R4" t="n">
-        <v>6812473</v>
+        <v>6812792</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302665</v>
+        <v>122302603</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,11 +984,6 @@
       <c r="E5" t="n">
         <v>6425</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455420</v>
+        <v>455413</v>
       </c>
       <c r="R5" t="n">
-        <v>6812744</v>
+        <v>6812351</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1083,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302655</v>
+        <v>122302748</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,11 +1081,6 @@
       <c r="E6" t="n">
         <v>6425</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455201</v>
+        <v>455119</v>
       </c>
       <c r="R6" t="n">
-        <v>6812767</v>
+        <v>6812489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302604</v>
+        <v>122302650</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1203,11 +1178,6 @@
       <c r="E7" t="n">
         <v>6425</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455405</v>
+        <v>455089</v>
       </c>
       <c r="R7" t="n">
-        <v>6812359</v>
+        <v>6812828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1220,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1287,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302583</v>
+        <v>122302727</v>
       </c>
       <c r="B8" t="n">
-        <v>78388</v>
+        <v>78652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1273,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455177</v>
+        <v>455408</v>
       </c>
       <c r="R8" t="n">
-        <v>6812448</v>
+        <v>6812407</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1317,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1389,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302752</v>
+        <v>122302583</v>
       </c>
       <c r="B9" t="n">
-        <v>78651</v>
+        <v>78389</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1370,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>228912</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454985</v>
+        <v>455177</v>
       </c>
       <c r="R9" t="n">
-        <v>6812455</v>
+        <v>6812448</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302658</v>
+        <v>122302579</v>
       </c>
       <c r="B10" t="n">
-        <v>78651</v>
+        <v>78389</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1467,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>228912</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455259</v>
+        <v>455212</v>
       </c>
       <c r="R10" t="n">
-        <v>6812731</v>
+        <v>6812763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302747</v>
+        <v>122302584</v>
       </c>
       <c r="B11" t="n">
-        <v>78651</v>
+        <v>78389</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1564,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>228912</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455137</v>
+        <v>455165</v>
       </c>
       <c r="R11" t="n">
-        <v>6812474</v>
+        <v>6812417</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302668</v>
+        <v>122302737</v>
       </c>
       <c r="B12" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1713,11 +1663,6 @@
       <c r="E12" t="n">
         <v>6425</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455485</v>
+        <v>455267</v>
       </c>
       <c r="R12" t="n">
-        <v>6812754</v>
+        <v>6812474</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302727</v>
+        <v>122302674</v>
       </c>
       <c r="B13" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1815,11 +1760,6 @@
       <c r="E13" t="n">
         <v>6425</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455408</v>
+        <v>455758</v>
       </c>
       <c r="R13" t="n">
-        <v>6812407</v>
+        <v>6812559</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,7 +1802,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1899,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302674</v>
+        <v>122302585</v>
       </c>
       <c r="B14" t="n">
-        <v>78651</v>
+        <v>78389</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1855,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>228912</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455758</v>
+        <v>454995</v>
       </c>
       <c r="R14" t="n">
-        <v>6812559</v>
+        <v>6812454</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302726</v>
+        <v>122302659</v>
       </c>
       <c r="B15" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2019,11 +1954,6 @@
       <c r="E15" t="n">
         <v>6425</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455407</v>
+        <v>455293</v>
       </c>
       <c r="R15" t="n">
-        <v>6812392</v>
+        <v>6812728</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +1996,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2103,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302745</v>
+        <v>122302669</v>
       </c>
       <c r="B16" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2121,11 +2051,6 @@
       <c r="E16" t="n">
         <v>6425</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2143,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455154</v>
+        <v>455567</v>
       </c>
       <c r="R16" t="n">
-        <v>6812449</v>
+        <v>6812725</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302594</v>
+        <v>122302538</v>
       </c>
       <c r="B17" t="n">
-        <v>78387</v>
+        <v>79270</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2146,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
+        <v>6453</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455177</v>
+        <v>455290</v>
       </c>
       <c r="R17" t="n">
-        <v>6812448</v>
+        <v>6812727</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302749</v>
+        <v>122302754</v>
       </c>
       <c r="B18" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2325,11 +2245,6 @@
       <c r="E18" t="n">
         <v>6425</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2347,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455098</v>
+        <v>454970</v>
       </c>
       <c r="R18" t="n">
-        <v>6812474</v>
+        <v>6812456</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302552</v>
+        <v>122302744</v>
       </c>
       <c r="B19" t="n">
-        <v>78685</v>
+        <v>78652</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2340,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Violettgrå tagellav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455409</v>
+        <v>455165</v>
       </c>
       <c r="R19" t="n">
-        <v>6812375</v>
+        <v>6812443</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,7 +2384,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2511,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302737</v>
+        <v>122302667</v>
       </c>
       <c r="B20" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2529,11 +2439,6 @@
       <c r="E20" t="n">
         <v>6425</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2551,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455267</v>
+        <v>455438</v>
       </c>
       <c r="R20" t="n">
-        <v>6812474</v>
+        <v>6812744</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2616,7 +2521,7 @@
         <v>122302651</v>
       </c>
       <c r="B21" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,11 +2535,6 @@
       </c>
       <c r="E21" t="n">
         <v>6425</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2715,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302605</v>
+        <v>122302665</v>
       </c>
       <c r="B22" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2733,11 +2633,6 @@
       <c r="E22" t="n">
         <v>6425</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2755,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455043</v>
+        <v>455420</v>
       </c>
       <c r="R22" t="n">
-        <v>6812499</v>
+        <v>6812744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302657</v>
+        <v>122302605</v>
       </c>
       <c r="B23" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2835,11 +2730,6 @@
       <c r="E23" t="n">
         <v>6425</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2857,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455243</v>
+        <v>455043</v>
       </c>
       <c r="R23" t="n">
-        <v>6812747</v>
+        <v>6812499</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302671</v>
+        <v>122302749</v>
       </c>
       <c r="B24" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2937,11 +2827,6 @@
       <c r="E24" t="n">
         <v>6425</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2959,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455616</v>
+        <v>455098</v>
       </c>
       <c r="R24" t="n">
-        <v>6812570</v>
+        <v>6812474</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302748</v>
+        <v>122302746</v>
       </c>
       <c r="B25" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3039,11 +2924,6 @@
       <c r="E25" t="n">
         <v>6425</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3061,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455119</v>
+        <v>455138</v>
       </c>
       <c r="R25" t="n">
-        <v>6812489</v>
+        <v>6812473</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302724</v>
+        <v>122302668</v>
       </c>
       <c r="B26" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3141,11 +3021,6 @@
       <c r="E26" t="n">
         <v>6425</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3163,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455449</v>
+        <v>455485</v>
       </c>
       <c r="R26" t="n">
-        <v>6812352</v>
+        <v>6812754</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,7 +3063,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3225,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302656</v>
+        <v>122302725</v>
       </c>
       <c r="B27" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3243,11 +3118,6 @@
       <c r="E27" t="n">
         <v>6425</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3265,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455229</v>
+        <v>455413</v>
       </c>
       <c r="R27" t="n">
-        <v>6812759</v>
+        <v>6812371</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,7 +3160,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3327,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302773</v>
+        <v>122302552</v>
       </c>
       <c r="B28" t="n">
-        <v>78035</v>
+        <v>78686</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3213,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
+        <v>185</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454992</v>
+        <v>455409</v>
       </c>
       <c r="R28" t="n">
-        <v>6812487</v>
+        <v>6812375</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,7 +3257,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3429,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122302673</v>
+        <v>122302671</v>
       </c>
       <c r="B29" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3447,11 +3312,6 @@
       <c r="E29" t="n">
         <v>6425</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3469,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455747</v>
+        <v>455616</v>
       </c>
       <c r="R29" t="n">
-        <v>6812550</v>
+        <v>6812570</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302725</v>
+        <v>122302743</v>
       </c>
       <c r="B30" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3549,11 +3409,6 @@
       <c r="E30" t="n">
         <v>6425</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3571,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455413</v>
+        <v>455165</v>
       </c>
       <c r="R30" t="n">
-        <v>6812371</v>
+        <v>6812417</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3596,7 +3451,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3633,10 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302753</v>
+        <v>122302654</v>
       </c>
       <c r="B31" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3651,11 +3506,6 @@
       <c r="E31" t="n">
         <v>6425</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3673,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454977</v>
+        <v>455187</v>
       </c>
       <c r="R31" t="n">
-        <v>6812451</v>
+        <v>6812780</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302653</v>
+        <v>122302751</v>
       </c>
       <c r="B32" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3753,11 +3603,6 @@
       <c r="E32" t="n">
         <v>6425</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3775,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455173</v>
+        <v>454998</v>
       </c>
       <c r="R32" t="n">
-        <v>6812786</v>
+        <v>6812459</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122302538</v>
+        <v>122302666</v>
       </c>
       <c r="B33" t="n">
-        <v>79269</v>
+        <v>78652</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3698,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455290</v>
+        <v>455428</v>
       </c>
       <c r="R33" t="n">
-        <v>6812727</v>
+        <v>6812747</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3779,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122302750</v>
+        <v>122302747</v>
       </c>
       <c r="B34" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3957,11 +3797,6 @@
       <c r="E34" t="n">
         <v>6425</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3979,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455083</v>
+        <v>455137</v>
       </c>
       <c r="R34" t="n">
-        <v>6812476</v>
+        <v>6812474</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122302672</v>
+        <v>122302670</v>
       </c>
       <c r="B35" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4059,11 +3894,6 @@
       <c r="E35" t="n">
         <v>6425</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4081,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455638</v>
+        <v>455615</v>
       </c>
       <c r="R35" t="n">
-        <v>6812544</v>
+        <v>6812587</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +3973,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122302659</v>
+        <v>122302736</v>
       </c>
       <c r="B36" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,11 +3991,6 @@
       <c r="E36" t="n">
         <v>6425</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4183,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455293</v>
+        <v>455295</v>
       </c>
       <c r="R36" t="n">
-        <v>6812728</v>
+        <v>6812491</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4070,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302754</v>
+        <v>122302752</v>
       </c>
       <c r="B37" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4263,11 +4088,6 @@
       <c r="E37" t="n">
         <v>6425</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4285,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454970</v>
+        <v>454985</v>
       </c>
       <c r="R37" t="n">
-        <v>6812456</v>
+        <v>6812455</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302743</v>
+        <v>122302658</v>
       </c>
       <c r="B38" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4365,11 +4185,6 @@
       <c r="E38" t="n">
         <v>6425</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4387,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455165</v>
+        <v>455259</v>
       </c>
       <c r="R38" t="n">
-        <v>6812417</v>
+        <v>6812731</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,7 +4264,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302579</v>
+        <v>122302594</v>
       </c>
       <c r="B39" t="n">
         <v>78388</v>
@@ -4465,21 +4280,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>6446</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455212</v>
+        <v>455177</v>
       </c>
       <c r="R39" t="n">
-        <v>6812763</v>
+        <v>6812448</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,10 +4361,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122302654</v>
+        <v>122302745</v>
       </c>
       <c r="B40" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4569,11 +4379,6 @@
       <c r="E40" t="n">
         <v>6425</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4591,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455187</v>
+        <v>455154</v>
       </c>
       <c r="R40" t="n">
-        <v>6812780</v>
+        <v>6812449</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4458,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302585</v>
+        <v>122302753</v>
       </c>
       <c r="B41" t="n">
-        <v>78388</v>
+        <v>78652</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4474,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454995</v>
+        <v>454977</v>
       </c>
       <c r="R41" t="n">
-        <v>6812454</v>
+        <v>6812451</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,10 +4555,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302670</v>
+        <v>122302773</v>
       </c>
       <c r="B42" t="n">
-        <v>78651</v>
+        <v>78036</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4571,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6437</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455615</v>
+        <v>454992</v>
       </c>
       <c r="R42" t="n">
-        <v>6812587</v>
+        <v>6812487</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,10 +4652,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302652</v>
+        <v>122302750</v>
       </c>
       <c r="B43" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4875,11 +4670,6 @@
       <c r="E43" t="n">
         <v>6425</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4897,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455165</v>
+        <v>455083</v>
       </c>
       <c r="R43" t="n">
-        <v>6812792</v>
+        <v>6812476</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,10 +4749,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302667</v>
+        <v>122302724</v>
       </c>
       <c r="B44" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4977,11 +4767,6 @@
       <c r="E44" t="n">
         <v>6425</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4999,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455438</v>
+        <v>455449</v>
       </c>
       <c r="R44" t="n">
-        <v>6812744</v>
+        <v>6812352</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5024,7 +4809,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5061,10 +4846,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302537</v>
+        <v>122302672</v>
       </c>
       <c r="B45" t="n">
-        <v>79269</v>
+        <v>78652</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,21 +4862,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455203</v>
+        <v>455638</v>
       </c>
       <c r="R45" t="n">
-        <v>6812760</v>
+        <v>6812544</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,10 +4943,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122302744</v>
+        <v>122302653</v>
       </c>
       <c r="B46" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5181,11 +4961,6 @@
       <c r="E46" t="n">
         <v>6425</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -5203,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455165</v>
+        <v>455173</v>
       </c>
       <c r="R46" t="n">
-        <v>6812443</v>
+        <v>6812786</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5265,10 +5040,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122302669</v>
+        <v>122302656</v>
       </c>
       <c r="B47" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5283,11 +5058,6 @@
       <c r="E47" t="n">
         <v>6425</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -5305,10 +5075,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455567</v>
+        <v>455229</v>
       </c>
       <c r="R47" t="n">
-        <v>6812725</v>
+        <v>6812759</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,10 +5137,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302553</v>
+        <v>122302726</v>
       </c>
       <c r="B48" t="n">
-        <v>79240</v>
+        <v>78652</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5383,21 +5153,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5407,10 +5172,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455736</v>
+        <v>455407</v>
       </c>
       <c r="R48" t="n">
-        <v>6812556</v>
+        <v>6812392</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5432,7 +5197,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5469,10 +5234,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122302736</v>
+        <v>122302655</v>
       </c>
       <c r="B49" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5487,11 +5252,6 @@
       <c r="E49" t="n">
         <v>6425</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -5509,10 +5269,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455295</v>
+        <v>455201</v>
       </c>
       <c r="R49" t="n">
-        <v>6812491</v>
+        <v>6812767</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,10 +5331,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122302650</v>
+        <v>122302537</v>
       </c>
       <c r="B50" t="n">
-        <v>78651</v>
+        <v>79270</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5587,21 +5347,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6453</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5611,10 +5366,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455089</v>
+        <v>455203</v>
       </c>
       <c r="R50" t="n">
-        <v>6812828</v>
+        <v>6812760</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,10 +5428,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302603</v>
+        <v>122302673</v>
       </c>
       <c r="B51" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5691,11 +5446,6 @@
       <c r="E51" t="n">
         <v>6425</v>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -5713,10 +5463,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455413</v>
+        <v>455747</v>
       </c>
       <c r="R51" t="n">
-        <v>6812351</v>
+        <v>6812550</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5488,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -5775,10 +5525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302666</v>
+        <v>122302553</v>
       </c>
       <c r="B52" t="n">
-        <v>78651</v>
+        <v>79241</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5791,21 +5541,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>229821</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5815,10 +5560,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455428</v>
+        <v>455736</v>
       </c>
       <c r="R52" t="n">
-        <v>6812747</v>
+        <v>6812556</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302746</v>
+        <v>122302552</v>
       </c>
       <c r="B25" t="n">
-        <v>78652</v>
+        <v>78686</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2922,16 +2922,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455138</v>
+        <v>455409</v>
       </c>
       <c r="R25" t="n">
-        <v>6812473</v>
+        <v>6812375</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3003,7 +3003,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302668</v>
+        <v>122302746</v>
       </c>
       <c r="B26" t="n">
         <v>78652</v>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455485</v>
+        <v>455138</v>
       </c>
       <c r="R26" t="n">
-        <v>6812754</v>
+        <v>6812473</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,7 +3100,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302725</v>
+        <v>122302668</v>
       </c>
       <c r="B27" t="n">
         <v>78652</v>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455413</v>
+        <v>455485</v>
       </c>
       <c r="R27" t="n">
-        <v>6812371</v>
+        <v>6812754</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302552</v>
+        <v>122302725</v>
       </c>
       <c r="B28" t="n">
-        <v>78686</v>
+        <v>78652</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3213,16 +3213,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455409</v>
+        <v>455413</v>
       </c>
       <c r="R28" t="n">
-        <v>6812375</v>
+        <v>6812371</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -5428,10 +5428,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302673</v>
+        <v>122302553</v>
       </c>
       <c r="B51" t="n">
-        <v>78652</v>
+        <v>79241</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5444,16 +5444,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455747</v>
+        <v>455736</v>
       </c>
       <c r="R51" t="n">
-        <v>6812550</v>
+        <v>6812556</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5525,10 +5525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302553</v>
+        <v>122302673</v>
       </c>
       <c r="B52" t="n">
-        <v>79241</v>
+        <v>78652</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5541,16 +5541,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455736</v>
+        <v>455747</v>
       </c>
       <c r="R52" t="n">
-        <v>6812556</v>
+        <v>6812550</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -5428,10 +5428,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302553</v>
+        <v>122302673</v>
       </c>
       <c r="B51" t="n">
-        <v>79241</v>
+        <v>78652</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5444,16 +5444,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455736</v>
+        <v>455747</v>
       </c>
       <c r="R51" t="n">
-        <v>6812556</v>
+        <v>6812550</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5525,10 +5525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302673</v>
+        <v>122302553</v>
       </c>
       <c r="B52" t="n">
-        <v>78652</v>
+        <v>79241</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5541,16 +5541,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455747</v>
+        <v>455736</v>
       </c>
       <c r="R52" t="n">
-        <v>6812550</v>
+        <v>6812556</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302604</v>
+        <v>122302669</v>
       </c>
       <c r="B2" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>6425</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455405</v>
+        <v>455567</v>
       </c>
       <c r="R2" t="n">
-        <v>6812359</v>
+        <v>6812725</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,7 +740,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302657</v>
+        <v>122302725</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,6 +795,11 @@
       <c r="E3" t="n">
         <v>6425</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455243</v>
+        <v>455413</v>
       </c>
       <c r="R3" t="n">
-        <v>6812747</v>
+        <v>6812371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -832,7 +842,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302652</v>
+        <v>122302751</v>
       </c>
       <c r="B4" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -887,6 +897,11 @@
       <c r="E4" t="n">
         <v>6425</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -904,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455165</v>
+        <v>454998</v>
       </c>
       <c r="R4" t="n">
-        <v>6812792</v>
+        <v>6812459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302603</v>
+        <v>122302665</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -984,6 +999,11 @@
       <c r="E5" t="n">
         <v>6425</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1001,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455413</v>
+        <v>455420</v>
       </c>
       <c r="R5" t="n">
-        <v>6812351</v>
+        <v>6812744</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1026,7 +1046,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1063,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302748</v>
+        <v>122302651</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1081,6 +1101,11 @@
       <c r="E6" t="n">
         <v>6425</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1101,7 +1126,7 @@
         <v>455119</v>
       </c>
       <c r="R6" t="n">
-        <v>6812489</v>
+        <v>6812817</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302650</v>
+        <v>122302727</v>
       </c>
       <c r="B7" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1178,6 +1203,11 @@
       <c r="E7" t="n">
         <v>6425</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1195,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455089</v>
+        <v>455408</v>
       </c>
       <c r="R7" t="n">
-        <v>6812828</v>
+        <v>6812407</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1220,7 +1250,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1257,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302727</v>
+        <v>122302753</v>
       </c>
       <c r="B8" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1275,6 +1305,11 @@
       <c r="E8" t="n">
         <v>6425</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1292,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455408</v>
+        <v>454977</v>
       </c>
       <c r="R8" t="n">
-        <v>6812407</v>
+        <v>6812451</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1317,7 +1352,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1354,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302583</v>
+        <v>122302747</v>
       </c>
       <c r="B9" t="n">
-        <v>78389</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1370,16 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455177</v>
+        <v>455137</v>
       </c>
       <c r="R9" t="n">
-        <v>6812448</v>
+        <v>6812474</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302579</v>
+        <v>122302743</v>
       </c>
       <c r="B10" t="n">
-        <v>78389</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1467,16 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455212</v>
+        <v>455165</v>
       </c>
       <c r="R10" t="n">
-        <v>6812763</v>
+        <v>6812417</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302584</v>
+        <v>122302656</v>
       </c>
       <c r="B11" t="n">
-        <v>78389</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1564,16 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455165</v>
+        <v>455229</v>
       </c>
       <c r="R11" t="n">
-        <v>6812417</v>
+        <v>6812759</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302737</v>
+        <v>122302650</v>
       </c>
       <c r="B12" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1663,6 +1713,11 @@
       <c r="E12" t="n">
         <v>6425</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1680,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455267</v>
+        <v>455089</v>
       </c>
       <c r="R12" t="n">
-        <v>6812474</v>
+        <v>6812828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302674</v>
+        <v>122302605</v>
       </c>
       <c r="B13" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1760,6 +1815,11 @@
       <c r="E13" t="n">
         <v>6425</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1777,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455758</v>
+        <v>455043</v>
       </c>
       <c r="R13" t="n">
-        <v>6812559</v>
+        <v>6812499</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302585</v>
+        <v>122302750</v>
       </c>
       <c r="B14" t="n">
-        <v>78389</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1855,16 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454995</v>
+        <v>455083</v>
       </c>
       <c r="R14" t="n">
-        <v>6812454</v>
+        <v>6812476</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302659</v>
+        <v>122302726</v>
       </c>
       <c r="B15" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1954,6 +2019,11 @@
       <c r="E15" t="n">
         <v>6425</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -1971,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455293</v>
+        <v>455407</v>
       </c>
       <c r="R15" t="n">
-        <v>6812728</v>
+        <v>6812392</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -1996,7 +2066,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2033,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302669</v>
+        <v>122302752</v>
       </c>
       <c r="B16" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2051,6 +2121,11 @@
       <c r="E16" t="n">
         <v>6425</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2068,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455567</v>
+        <v>454985</v>
       </c>
       <c r="R16" t="n">
-        <v>6812725</v>
+        <v>6812455</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302538</v>
+        <v>122302744</v>
       </c>
       <c r="B17" t="n">
-        <v>79270</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2146,16 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455290</v>
+        <v>455165</v>
       </c>
       <c r="R17" t="n">
-        <v>6812727</v>
+        <v>6812443</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302754</v>
+        <v>122302655</v>
       </c>
       <c r="B18" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2245,6 +2325,11 @@
       <c r="E18" t="n">
         <v>6425</v>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2262,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454970</v>
+        <v>455201</v>
       </c>
       <c r="R18" t="n">
-        <v>6812456</v>
+        <v>6812767</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302744</v>
+        <v>122302667</v>
       </c>
       <c r="B19" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2342,6 +2427,11 @@
       <c r="E19" t="n">
         <v>6425</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2359,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455165</v>
+        <v>455438</v>
       </c>
       <c r="R19" t="n">
-        <v>6812443</v>
+        <v>6812744</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302667</v>
+        <v>122302674</v>
       </c>
       <c r="B20" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2439,6 +2529,11 @@
       <c r="E20" t="n">
         <v>6425</v>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2456,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455438</v>
+        <v>455758</v>
       </c>
       <c r="R20" t="n">
-        <v>6812744</v>
+        <v>6812559</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302651</v>
+        <v>122302748</v>
       </c>
       <c r="B21" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2536,6 +2631,11 @@
       <c r="E21" t="n">
         <v>6425</v>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2556,7 +2656,7 @@
         <v>455119</v>
       </c>
       <c r="R21" t="n">
-        <v>6812817</v>
+        <v>6812489</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302665</v>
+        <v>122302670</v>
       </c>
       <c r="B22" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2633,6 +2733,11 @@
       <c r="E22" t="n">
         <v>6425</v>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2650,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455420</v>
+        <v>455615</v>
       </c>
       <c r="R22" t="n">
-        <v>6812744</v>
+        <v>6812587</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302605</v>
+        <v>122302724</v>
       </c>
       <c r="B23" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2730,6 +2835,11 @@
       <c r="E23" t="n">
         <v>6425</v>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2747,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455043</v>
+        <v>455449</v>
       </c>
       <c r="R23" t="n">
-        <v>6812499</v>
+        <v>6812352</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2772,7 +2882,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2809,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302749</v>
+        <v>122302736</v>
       </c>
       <c r="B24" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2827,6 +2937,11 @@
       <c r="E24" t="n">
         <v>6425</v>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -2844,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455098</v>
+        <v>455295</v>
       </c>
       <c r="R24" t="n">
-        <v>6812474</v>
+        <v>6812491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302552</v>
+        <v>122302666</v>
       </c>
       <c r="B25" t="n">
-        <v>78686</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2922,16 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455409</v>
+        <v>455428</v>
       </c>
       <c r="R25" t="n">
-        <v>6812375</v>
+        <v>6812747</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2966,7 +3086,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3003,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302746</v>
+        <v>122302673</v>
       </c>
       <c r="B26" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3021,6 +3141,11 @@
       <c r="E26" t="n">
         <v>6425</v>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3038,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455138</v>
+        <v>455747</v>
       </c>
       <c r="R26" t="n">
-        <v>6812473</v>
+        <v>6812550</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3100,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302668</v>
+        <v>122302657</v>
       </c>
       <c r="B27" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3118,6 +3243,11 @@
       <c r="E27" t="n">
         <v>6425</v>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3135,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455485</v>
+        <v>455243</v>
       </c>
       <c r="R27" t="n">
-        <v>6812754</v>
+        <v>6812747</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3197,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302725</v>
+        <v>122302737</v>
       </c>
       <c r="B28" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3215,6 +3345,11 @@
       <c r="E28" t="n">
         <v>6425</v>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3232,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455413</v>
+        <v>455267</v>
       </c>
       <c r="R28" t="n">
-        <v>6812371</v>
+        <v>6812474</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3257,7 +3392,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3294,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122302671</v>
+        <v>122302583</v>
       </c>
       <c r="B29" t="n">
-        <v>78652</v>
+        <v>78393</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3310,16 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3329,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455616</v>
+        <v>455177</v>
       </c>
       <c r="R29" t="n">
-        <v>6812570</v>
+        <v>6812448</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3391,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302743</v>
+        <v>122302579</v>
       </c>
       <c r="B30" t="n">
-        <v>78652</v>
+        <v>78393</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3407,16 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3426,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455165</v>
+        <v>455212</v>
       </c>
       <c r="R30" t="n">
-        <v>6812417</v>
+        <v>6812763</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3488,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302654</v>
+        <v>122302746</v>
       </c>
       <c r="B31" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3506,6 +3651,11 @@
       <c r="E31" t="n">
         <v>6425</v>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3523,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455187</v>
+        <v>455138</v>
       </c>
       <c r="R31" t="n">
-        <v>6812780</v>
+        <v>6812473</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3585,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302751</v>
+        <v>122302749</v>
       </c>
       <c r="B32" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3603,6 +3753,11 @@
       <c r="E32" t="n">
         <v>6425</v>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3620,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454998</v>
+        <v>455098</v>
       </c>
       <c r="R32" t="n">
-        <v>6812459</v>
+        <v>6812474</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3682,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122302666</v>
+        <v>122302552</v>
       </c>
       <c r="B33" t="n">
-        <v>78652</v>
+        <v>78690</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3698,16 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>185</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3717,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455428</v>
+        <v>455409</v>
       </c>
       <c r="R33" t="n">
-        <v>6812747</v>
+        <v>6812375</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3742,7 +3902,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3779,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122302747</v>
+        <v>122302654</v>
       </c>
       <c r="B34" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3797,6 +3957,11 @@
       <c r="E34" t="n">
         <v>6425</v>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -3814,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455137</v>
+        <v>455187</v>
       </c>
       <c r="R34" t="n">
-        <v>6812474</v>
+        <v>6812780</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3876,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122302670</v>
+        <v>122302594</v>
       </c>
       <c r="B35" t="n">
-        <v>78652</v>
+        <v>78392</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3892,16 +4057,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3911,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455615</v>
+        <v>455177</v>
       </c>
       <c r="R35" t="n">
-        <v>6812587</v>
+        <v>6812448</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3973,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122302736</v>
+        <v>122302537</v>
       </c>
       <c r="B36" t="n">
-        <v>78652</v>
+        <v>79274</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -3989,16 +4159,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4008,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455295</v>
+        <v>455203</v>
       </c>
       <c r="R36" t="n">
-        <v>6812491</v>
+        <v>6812760</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4070,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302752</v>
+        <v>122302585</v>
       </c>
       <c r="B37" t="n">
-        <v>78652</v>
+        <v>78393</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4086,16 +4261,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4105,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454985</v>
+        <v>454995</v>
       </c>
       <c r="R37" t="n">
-        <v>6812455</v>
+        <v>6812454</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302658</v>
+        <v>122302538</v>
       </c>
       <c r="B38" t="n">
-        <v>78652</v>
+        <v>79274</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4183,16 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4202,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455259</v>
+        <v>455290</v>
       </c>
       <c r="R38" t="n">
-        <v>6812731</v>
+        <v>6812727</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4264,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302594</v>
+        <v>122302671</v>
       </c>
       <c r="B39" t="n">
-        <v>78388</v>
+        <v>78656</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4280,16 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4299,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455177</v>
+        <v>455616</v>
       </c>
       <c r="R39" t="n">
-        <v>6812448</v>
+        <v>6812570</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4361,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122302745</v>
+        <v>122302584</v>
       </c>
       <c r="B40" t="n">
-        <v>78652</v>
+        <v>78393</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4377,16 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4396,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455154</v>
+        <v>455165</v>
       </c>
       <c r="R40" t="n">
-        <v>6812449</v>
+        <v>6812417</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4458,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302753</v>
+        <v>122302754</v>
       </c>
       <c r="B41" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4476,6 +4671,11 @@
       <c r="E41" t="n">
         <v>6425</v>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4493,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454977</v>
+        <v>454970</v>
       </c>
       <c r="R41" t="n">
-        <v>6812451</v>
+        <v>6812456</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4558,7 +4758,7 @@
         <v>122302773</v>
       </c>
       <c r="B42" t="n">
-        <v>78036</v>
+        <v>78040</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4572,6 +4772,11 @@
       </c>
       <c r="E42" t="n">
         <v>6437</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4652,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302750</v>
+        <v>122302658</v>
       </c>
       <c r="B43" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4670,6 +4875,11 @@
       <c r="E43" t="n">
         <v>6425</v>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4687,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455083</v>
+        <v>455259</v>
       </c>
       <c r="R43" t="n">
-        <v>6812476</v>
+        <v>6812731</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4749,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302724</v>
+        <v>122302603</v>
       </c>
       <c r="B44" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4767,6 +4977,11 @@
       <c r="E44" t="n">
         <v>6425</v>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4784,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455449</v>
+        <v>455413</v>
       </c>
       <c r="R44" t="n">
-        <v>6812352</v>
+        <v>6812351</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4846,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302672</v>
+        <v>122302604</v>
       </c>
       <c r="B45" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -4864,6 +5079,11 @@
       <c r="E45" t="n">
         <v>6425</v>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4881,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455638</v>
+        <v>455405</v>
       </c>
       <c r="R45" t="n">
-        <v>6812544</v>
+        <v>6812359</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4906,7 +5126,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -4943,10 +5163,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122302653</v>
+        <v>122302745</v>
       </c>
       <c r="B46" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -4961,6 +5181,11 @@
       <c r="E46" t="n">
         <v>6425</v>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4978,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455173</v>
+        <v>455154</v>
       </c>
       <c r="R46" t="n">
-        <v>6812786</v>
+        <v>6812449</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5040,10 +5265,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122302656</v>
+        <v>122302672</v>
       </c>
       <c r="B47" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5058,6 +5283,11 @@
       <c r="E47" t="n">
         <v>6425</v>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -5075,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455229</v>
+        <v>455638</v>
       </c>
       <c r="R47" t="n">
-        <v>6812759</v>
+        <v>6812544</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5137,10 +5367,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302726</v>
+        <v>122302659</v>
       </c>
       <c r="B48" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5155,6 +5385,11 @@
       <c r="E48" t="n">
         <v>6425</v>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -5172,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455407</v>
+        <v>455293</v>
       </c>
       <c r="R48" t="n">
-        <v>6812392</v>
+        <v>6812728</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5197,7 +5432,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -5234,10 +5469,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122302655</v>
+        <v>122302652</v>
       </c>
       <c r="B49" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5252,6 +5487,11 @@
       <c r="E49" t="n">
         <v>6425</v>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -5269,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455201</v>
+        <v>455165</v>
       </c>
       <c r="R49" t="n">
-        <v>6812767</v>
+        <v>6812792</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5331,10 +5571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122302537</v>
+        <v>122302553</v>
       </c>
       <c r="B50" t="n">
-        <v>79270</v>
+        <v>79245</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5347,16 +5587,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>229821</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5366,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455203</v>
+        <v>455736</v>
       </c>
       <c r="R50" t="n">
-        <v>6812760</v>
+        <v>6812556</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5428,10 +5673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302673</v>
+        <v>122302653</v>
       </c>
       <c r="B51" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5446,6 +5691,11 @@
       <c r="E51" t="n">
         <v>6425</v>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -5463,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455747</v>
+        <v>455173</v>
       </c>
       <c r="R51" t="n">
-        <v>6812550</v>
+        <v>6812786</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5525,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302553</v>
+        <v>122302668</v>
       </c>
       <c r="B52" t="n">
-        <v>79241</v>
+        <v>78656</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5541,16 +5791,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5560,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455736</v>
+        <v>455485</v>
       </c>
       <c r="R52" t="n">
-        <v>6812556</v>
+        <v>6812754</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302669</v>
+        <v>122302670</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455567</v>
+        <v>455615</v>
       </c>
       <c r="R2" t="n">
-        <v>6812725</v>
+        <v>6812587</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302725</v>
+        <v>122302673</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455413</v>
+        <v>455747</v>
       </c>
       <c r="R3" t="n">
-        <v>6812371</v>
+        <v>6812550</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302751</v>
+        <v>122302746</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454998</v>
+        <v>455138</v>
       </c>
       <c r="R4" t="n">
-        <v>6812459</v>
+        <v>6812473</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302665</v>
+        <v>122302748</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455420</v>
+        <v>455119</v>
       </c>
       <c r="R5" t="n">
-        <v>6812744</v>
+        <v>6812489</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302651</v>
+        <v>122302584</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455119</v>
+        <v>455165</v>
       </c>
       <c r="R6" t="n">
-        <v>6812817</v>
+        <v>6812417</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302727</v>
+        <v>122302750</v>
       </c>
       <c r="B7" t="n">
         <v>78656</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455408</v>
+        <v>455083</v>
       </c>
       <c r="R7" t="n">
-        <v>6812407</v>
+        <v>6812476</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302753</v>
+        <v>122302749</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454977</v>
+        <v>455098</v>
       </c>
       <c r="R8" t="n">
-        <v>6812451</v>
+        <v>6812474</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302747</v>
+        <v>122302725</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455137</v>
+        <v>455413</v>
       </c>
       <c r="R9" t="n">
-        <v>6812474</v>
+        <v>6812371</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302743</v>
+        <v>122302538</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455165</v>
+        <v>455290</v>
       </c>
       <c r="R10" t="n">
-        <v>6812417</v>
+        <v>6812727</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302656</v>
+        <v>122302745</v>
       </c>
       <c r="B11" t="n">
         <v>78656</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455229</v>
+        <v>455154</v>
       </c>
       <c r="R11" t="n">
-        <v>6812759</v>
+        <v>6812449</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302650</v>
+        <v>122302667</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455089</v>
+        <v>455438</v>
       </c>
       <c r="R12" t="n">
-        <v>6812828</v>
+        <v>6812744</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302605</v>
+        <v>122302752</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455043</v>
+        <v>454985</v>
       </c>
       <c r="R13" t="n">
-        <v>6812499</v>
+        <v>6812455</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302750</v>
+        <v>122302583</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455083</v>
+        <v>455177</v>
       </c>
       <c r="R14" t="n">
-        <v>6812476</v>
+        <v>6812448</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302726</v>
+        <v>122302736</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455407</v>
+        <v>455295</v>
       </c>
       <c r="R15" t="n">
-        <v>6812392</v>
+        <v>6812491</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302752</v>
+        <v>122302657</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454985</v>
+        <v>455243</v>
       </c>
       <c r="R16" t="n">
-        <v>6812455</v>
+        <v>6812747</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302744</v>
+        <v>122302658</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455165</v>
+        <v>455259</v>
       </c>
       <c r="R17" t="n">
-        <v>6812443</v>
+        <v>6812731</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302655</v>
+        <v>122302552</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455201</v>
+        <v>455409</v>
       </c>
       <c r="R18" t="n">
-        <v>6812767</v>
+        <v>6812375</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302667</v>
+        <v>122302724</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455438</v>
+        <v>455449</v>
       </c>
       <c r="R19" t="n">
-        <v>6812744</v>
+        <v>6812352</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302674</v>
+        <v>122302666</v>
       </c>
       <c r="B20" t="n">
         <v>78656</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455758</v>
+        <v>455428</v>
       </c>
       <c r="R20" t="n">
-        <v>6812559</v>
+        <v>6812747</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302748</v>
+        <v>122302655</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455119</v>
+        <v>455201</v>
       </c>
       <c r="R21" t="n">
-        <v>6812489</v>
+        <v>6812767</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302670</v>
+        <v>122302665</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455615</v>
+        <v>455420</v>
       </c>
       <c r="R22" t="n">
-        <v>6812587</v>
+        <v>6812744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302724</v>
+        <v>122302727</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455449</v>
+        <v>455408</v>
       </c>
       <c r="R23" t="n">
-        <v>6812352</v>
+        <v>6812407</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302736</v>
+        <v>122302753</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455295</v>
+        <v>454977</v>
       </c>
       <c r="R24" t="n">
-        <v>6812491</v>
+        <v>6812451</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302666</v>
+        <v>122302669</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455428</v>
+        <v>455567</v>
       </c>
       <c r="R25" t="n">
-        <v>6812747</v>
+        <v>6812725</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302673</v>
+        <v>122302754</v>
       </c>
       <c r="B26" t="n">
         <v>78656</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455747</v>
+        <v>454970</v>
       </c>
       <c r="R26" t="n">
-        <v>6812550</v>
+        <v>6812456</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302657</v>
+        <v>122302579</v>
       </c>
       <c r="B27" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455243</v>
+        <v>455212</v>
       </c>
       <c r="R27" t="n">
-        <v>6812747</v>
+        <v>6812763</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302737</v>
+        <v>122302553</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>79245</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455267</v>
+        <v>455736</v>
       </c>
       <c r="R28" t="n">
-        <v>6812474</v>
+        <v>6812556</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122302583</v>
+        <v>122302671</v>
       </c>
       <c r="B29" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455177</v>
+        <v>455616</v>
       </c>
       <c r="R29" t="n">
-        <v>6812448</v>
+        <v>6812570</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302579</v>
+        <v>122302650</v>
       </c>
       <c r="B30" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455212</v>
+        <v>455089</v>
       </c>
       <c r="R30" t="n">
-        <v>6812763</v>
+        <v>6812828</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302746</v>
+        <v>122302594</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>78392</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455138</v>
+        <v>455177</v>
       </c>
       <c r="R31" t="n">
-        <v>6812473</v>
+        <v>6812448</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302749</v>
+        <v>122302653</v>
       </c>
       <c r="B32" t="n">
         <v>78656</v>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455098</v>
+        <v>455173</v>
       </c>
       <c r="R32" t="n">
-        <v>6812474</v>
+        <v>6812786</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122302552</v>
+        <v>122302652</v>
       </c>
       <c r="B33" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455409</v>
+        <v>455165</v>
       </c>
       <c r="R33" t="n">
-        <v>6812375</v>
+        <v>6812792</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -3939,7 +3939,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122302654</v>
+        <v>122302751</v>
       </c>
       <c r="B34" t="n">
         <v>78656</v>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455187</v>
+        <v>454998</v>
       </c>
       <c r="R34" t="n">
-        <v>6812780</v>
+        <v>6812459</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122302594</v>
+        <v>122302674</v>
       </c>
       <c r="B35" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4057,21 +4057,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455177</v>
+        <v>455758</v>
       </c>
       <c r="R35" t="n">
-        <v>6812448</v>
+        <v>6812559</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122302537</v>
+        <v>122302659</v>
       </c>
       <c r="B36" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4159,21 +4159,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455203</v>
+        <v>455293</v>
       </c>
       <c r="R36" t="n">
-        <v>6812760</v>
+        <v>6812728</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302585</v>
+        <v>122302605</v>
       </c>
       <c r="B37" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4261,21 +4261,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454995</v>
+        <v>455043</v>
       </c>
       <c r="R37" t="n">
-        <v>6812454</v>
+        <v>6812499</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302538</v>
+        <v>122302726</v>
       </c>
       <c r="B38" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455290</v>
+        <v>455407</v>
       </c>
       <c r="R38" t="n">
-        <v>6812727</v>
+        <v>6812392</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4449,7 +4449,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302671</v>
+        <v>122302603</v>
       </c>
       <c r="B39" t="n">
         <v>78656</v>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455616</v>
+        <v>455413</v>
       </c>
       <c r="R39" t="n">
-        <v>6812570</v>
+        <v>6812351</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122302584</v>
+        <v>122302737</v>
       </c>
       <c r="B40" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455165</v>
+        <v>455267</v>
       </c>
       <c r="R40" t="n">
-        <v>6812417</v>
+        <v>6812474</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,7 +4653,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302754</v>
+        <v>122302672</v>
       </c>
       <c r="B41" t="n">
         <v>78656</v>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454970</v>
+        <v>455638</v>
       </c>
       <c r="R41" t="n">
-        <v>6812456</v>
+        <v>6812544</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302773</v>
+        <v>122302747</v>
       </c>
       <c r="B42" t="n">
-        <v>78040</v>
+        <v>78656</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454992</v>
+        <v>455137</v>
       </c>
       <c r="R42" t="n">
-        <v>6812487</v>
+        <v>6812474</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302658</v>
+        <v>122302604</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455259</v>
+        <v>455405</v>
       </c>
       <c r="R43" t="n">
-        <v>6812731</v>
+        <v>6812359</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -4959,7 +4959,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302603</v>
+        <v>122302656</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455413</v>
+        <v>455229</v>
       </c>
       <c r="R44" t="n">
-        <v>6812351</v>
+        <v>6812759</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5061,7 +5061,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302604</v>
+        <v>122302744</v>
       </c>
       <c r="B45" t="n">
         <v>78656</v>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455405</v>
+        <v>455165</v>
       </c>
       <c r="R45" t="n">
-        <v>6812359</v>
+        <v>6812443</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5163,7 +5163,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122302745</v>
+        <v>122302651</v>
       </c>
       <c r="B46" t="n">
         <v>78656</v>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455154</v>
+        <v>455119</v>
       </c>
       <c r="R46" t="n">
-        <v>6812449</v>
+        <v>6812817</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122302672</v>
+        <v>122302654</v>
       </c>
       <c r="B47" t="n">
         <v>78656</v>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455638</v>
+        <v>455187</v>
       </c>
       <c r="R47" t="n">
-        <v>6812544</v>
+        <v>6812780</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,10 +5367,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302659</v>
+        <v>122302585</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5383,21 +5383,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455293</v>
+        <v>454995</v>
       </c>
       <c r="R48" t="n">
-        <v>6812728</v>
+        <v>6812454</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5469,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122302652</v>
+        <v>122302773</v>
       </c>
       <c r="B49" t="n">
-        <v>78656</v>
+        <v>78040</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5485,21 +5485,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455165</v>
+        <v>454992</v>
       </c>
       <c r="R49" t="n">
-        <v>6812792</v>
+        <v>6812487</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,10 +5571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122302553</v>
+        <v>122302743</v>
       </c>
       <c r="B50" t="n">
-        <v>79245</v>
+        <v>78656</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455736</v>
+        <v>455165</v>
       </c>
       <c r="R50" t="n">
-        <v>6812556</v>
+        <v>6812417</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302653</v>
+        <v>122302537</v>
       </c>
       <c r="B51" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5689,21 +5689,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455173</v>
+        <v>455203</v>
       </c>
       <c r="R51" t="n">
-        <v>6812786</v>
+        <v>6812760</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302538</v>
+        <v>122302752</v>
       </c>
       <c r="B10" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455290</v>
+        <v>454985</v>
       </c>
       <c r="R10" t="n">
-        <v>6812727</v>
+        <v>6812455</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302745</v>
+        <v>122302538</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455154</v>
+        <v>455290</v>
       </c>
       <c r="R11" t="n">
-        <v>6812449</v>
+        <v>6812727</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302667</v>
+        <v>122302745</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455438</v>
+        <v>455154</v>
       </c>
       <c r="R12" t="n">
-        <v>6812744</v>
+        <v>6812449</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302752</v>
+        <v>122302667</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454985</v>
+        <v>455438</v>
       </c>
       <c r="R13" t="n">
-        <v>6812455</v>
+        <v>6812744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302724</v>
+        <v>122302655</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455449</v>
+        <v>455201</v>
       </c>
       <c r="R19" t="n">
-        <v>6812352</v>
+        <v>6812767</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302666</v>
+        <v>122302665</v>
       </c>
       <c r="B20" t="n">
         <v>78656</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455428</v>
+        <v>455420</v>
       </c>
       <c r="R20" t="n">
-        <v>6812747</v>
+        <v>6812744</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302655</v>
+        <v>122302727</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455201</v>
+        <v>455408</v>
       </c>
       <c r="R21" t="n">
-        <v>6812767</v>
+        <v>6812407</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302665</v>
+        <v>122302666</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455420</v>
+        <v>455428</v>
       </c>
       <c r="R22" t="n">
-        <v>6812744</v>
+        <v>6812747</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302727</v>
+        <v>122302724</v>
       </c>
       <c r="B23" t="n">
         <v>78656</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455408</v>
+        <v>455449</v>
       </c>
       <c r="R23" t="n">
-        <v>6812407</v>
+        <v>6812352</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302754</v>
+        <v>122302579</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454970</v>
+        <v>455212</v>
       </c>
       <c r="R26" t="n">
-        <v>6812456</v>
+        <v>6812763</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302579</v>
+        <v>122302553</v>
       </c>
       <c r="B27" t="n">
-        <v>78393</v>
+        <v>79245</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455212</v>
+        <v>455736</v>
       </c>
       <c r="R27" t="n">
-        <v>6812763</v>
+        <v>6812556</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302553</v>
+        <v>122302754</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455736</v>
+        <v>454970</v>
       </c>
       <c r="R28" t="n">
-        <v>6812556</v>
+        <v>6812456</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302605</v>
+        <v>122302726</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455043</v>
+        <v>455407</v>
       </c>
       <c r="R37" t="n">
-        <v>6812499</v>
+        <v>6812392</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4347,7 +4347,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302726</v>
+        <v>122302603</v>
       </c>
       <c r="B38" t="n">
         <v>78656</v>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455407</v>
+        <v>455413</v>
       </c>
       <c r="R38" t="n">
-        <v>6812392</v>
+        <v>6812351</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,7 +4449,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302603</v>
+        <v>122302605</v>
       </c>
       <c r="B39" t="n">
         <v>78656</v>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455413</v>
+        <v>455043</v>
       </c>
       <c r="R39" t="n">
-        <v>6812351</v>
+        <v>6812499</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302670</v>
+        <v>122302753</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455615</v>
+        <v>454977</v>
       </c>
       <c r="R2" t="n">
-        <v>6812587</v>
+        <v>6812451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302673</v>
+        <v>122302651</v>
       </c>
       <c r="B3" t="n">
         <v>78656</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455747</v>
+        <v>455119</v>
       </c>
       <c r="R3" t="n">
-        <v>6812550</v>
+        <v>6812817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302746</v>
+        <v>122302665</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455138</v>
+        <v>455420</v>
       </c>
       <c r="R4" t="n">
-        <v>6812473</v>
+        <v>6812744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302748</v>
+        <v>122302737</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455119</v>
+        <v>455267</v>
       </c>
       <c r="R5" t="n">
-        <v>6812489</v>
+        <v>6812474</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302584</v>
+        <v>122302674</v>
       </c>
       <c r="B6" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455165</v>
+        <v>455758</v>
       </c>
       <c r="R6" t="n">
-        <v>6812417</v>
+        <v>6812559</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302750</v>
+        <v>122302583</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455083</v>
+        <v>455177</v>
       </c>
       <c r="R7" t="n">
-        <v>6812476</v>
+        <v>6812448</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302749</v>
+        <v>122302748</v>
       </c>
       <c r="B8" t="n">
         <v>78656</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455098</v>
+        <v>455119</v>
       </c>
       <c r="R8" t="n">
-        <v>6812474</v>
+        <v>6812489</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302752</v>
+        <v>122302726</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454985</v>
+        <v>455407</v>
       </c>
       <c r="R10" t="n">
-        <v>6812455</v>
+        <v>6812392</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302538</v>
+        <v>122302553</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>79245</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455290</v>
+        <v>455736</v>
       </c>
       <c r="R11" t="n">
-        <v>6812727</v>
+        <v>6812556</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302745</v>
+        <v>122302650</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455154</v>
+        <v>455089</v>
       </c>
       <c r="R12" t="n">
-        <v>6812449</v>
+        <v>6812828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302667</v>
+        <v>122302670</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455438</v>
+        <v>455615</v>
       </c>
       <c r="R13" t="n">
-        <v>6812744</v>
+        <v>6812587</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302583</v>
+        <v>122302754</v>
       </c>
       <c r="B14" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455177</v>
+        <v>454970</v>
       </c>
       <c r="R14" t="n">
-        <v>6812448</v>
+        <v>6812456</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302736</v>
+        <v>122302657</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455295</v>
+        <v>455243</v>
       </c>
       <c r="R15" t="n">
-        <v>6812491</v>
+        <v>6812747</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302657</v>
+        <v>122302659</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455243</v>
+        <v>455293</v>
       </c>
       <c r="R16" t="n">
-        <v>6812747</v>
+        <v>6812728</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302658</v>
+        <v>122302743</v>
       </c>
       <c r="B17" t="n">
         <v>78656</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455259</v>
+        <v>455165</v>
       </c>
       <c r="R17" t="n">
-        <v>6812731</v>
+        <v>6812417</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302552</v>
+        <v>122302604</v>
       </c>
       <c r="B18" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455409</v>
+        <v>455405</v>
       </c>
       <c r="R18" t="n">
-        <v>6812375</v>
+        <v>6812359</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302655</v>
+        <v>122302652</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455201</v>
+        <v>455165</v>
       </c>
       <c r="R19" t="n">
-        <v>6812767</v>
+        <v>6812792</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302665</v>
+        <v>122302653</v>
       </c>
       <c r="B20" t="n">
         <v>78656</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455420</v>
+        <v>455173</v>
       </c>
       <c r="R20" t="n">
-        <v>6812744</v>
+        <v>6812786</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302727</v>
+        <v>122302655</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455408</v>
+        <v>455201</v>
       </c>
       <c r="R21" t="n">
-        <v>6812407</v>
+        <v>6812767</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302666</v>
+        <v>122302744</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455428</v>
+        <v>455165</v>
       </c>
       <c r="R22" t="n">
-        <v>6812747</v>
+        <v>6812443</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302724</v>
+        <v>122302584</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455449</v>
+        <v>455165</v>
       </c>
       <c r="R23" t="n">
-        <v>6812352</v>
+        <v>6812417</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302753</v>
+        <v>122302745</v>
       </c>
       <c r="B24" t="n">
         <v>78656</v>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454977</v>
+        <v>455154</v>
       </c>
       <c r="R24" t="n">
-        <v>6812451</v>
+        <v>6812449</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302669</v>
+        <v>122302656</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455567</v>
+        <v>455229</v>
       </c>
       <c r="R25" t="n">
-        <v>6812725</v>
+        <v>6812759</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302579</v>
+        <v>122302669</v>
       </c>
       <c r="B26" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455212</v>
+        <v>455567</v>
       </c>
       <c r="R26" t="n">
-        <v>6812763</v>
+        <v>6812725</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302553</v>
+        <v>122302667</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>78656</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455736</v>
+        <v>455438</v>
       </c>
       <c r="R27" t="n">
-        <v>6812556</v>
+        <v>6812744</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302754</v>
+        <v>122302773</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>78040</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454970</v>
+        <v>454992</v>
       </c>
       <c r="R28" t="n">
-        <v>6812456</v>
+        <v>6812487</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,7 +3429,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122302671</v>
+        <v>122302752</v>
       </c>
       <c r="B29" t="n">
         <v>78656</v>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455616</v>
+        <v>454985</v>
       </c>
       <c r="R29" t="n">
-        <v>6812570</v>
+        <v>6812455</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302650</v>
+        <v>122302658</v>
       </c>
       <c r="B30" t="n">
         <v>78656</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455089</v>
+        <v>455259</v>
       </c>
       <c r="R30" t="n">
-        <v>6812828</v>
+        <v>6812731</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302594</v>
+        <v>122302747</v>
       </c>
       <c r="B31" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455177</v>
+        <v>455137</v>
       </c>
       <c r="R31" t="n">
-        <v>6812448</v>
+        <v>6812474</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302653</v>
+        <v>122302727</v>
       </c>
       <c r="B32" t="n">
         <v>78656</v>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455173</v>
+        <v>455408</v>
       </c>
       <c r="R32" t="n">
-        <v>6812786</v>
+        <v>6812407</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3837,7 +3837,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122302652</v>
+        <v>122302666</v>
       </c>
       <c r="B33" t="n">
         <v>78656</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455165</v>
+        <v>455428</v>
       </c>
       <c r="R33" t="n">
-        <v>6812792</v>
+        <v>6812747</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122302751</v>
+        <v>122302736</v>
       </c>
       <c r="B34" t="n">
         <v>78656</v>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454998</v>
+        <v>455295</v>
       </c>
       <c r="R34" t="n">
-        <v>6812459</v>
+        <v>6812491</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122302674</v>
+        <v>122302668</v>
       </c>
       <c r="B35" t="n">
         <v>78656</v>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455758</v>
+        <v>455485</v>
       </c>
       <c r="R35" t="n">
-        <v>6812559</v>
+        <v>6812754</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122302659</v>
+        <v>122302605</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455293</v>
+        <v>455043</v>
       </c>
       <c r="R36" t="n">
-        <v>6812728</v>
+        <v>6812499</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302726</v>
+        <v>122302654</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455407</v>
+        <v>455187</v>
       </c>
       <c r="R37" t="n">
-        <v>6812392</v>
+        <v>6812780</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302603</v>
+        <v>122302537</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455413</v>
+        <v>455203</v>
       </c>
       <c r="R38" t="n">
-        <v>6812351</v>
+        <v>6812760</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4449,7 +4449,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302605</v>
+        <v>122302603</v>
       </c>
       <c r="B39" t="n">
         <v>78656</v>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455043</v>
+        <v>455413</v>
       </c>
       <c r="R39" t="n">
-        <v>6812499</v>
+        <v>6812351</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122302737</v>
+        <v>122302538</v>
       </c>
       <c r="B40" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455267</v>
+        <v>455290</v>
       </c>
       <c r="R40" t="n">
-        <v>6812474</v>
+        <v>6812727</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302672</v>
+        <v>122302552</v>
       </c>
       <c r="B41" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455638</v>
+        <v>455409</v>
       </c>
       <c r="R41" t="n">
-        <v>6812544</v>
+        <v>6812375</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4755,7 +4755,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302747</v>
+        <v>122302671</v>
       </c>
       <c r="B42" t="n">
         <v>78656</v>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455137</v>
+        <v>455616</v>
       </c>
       <c r="R42" t="n">
-        <v>6812474</v>
+        <v>6812570</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302604</v>
+        <v>122302724</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455405</v>
+        <v>455449</v>
       </c>
       <c r="R43" t="n">
-        <v>6812359</v>
+        <v>6812352</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302656</v>
+        <v>122302594</v>
       </c>
       <c r="B44" t="n">
-        <v>78656</v>
+        <v>78392</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455229</v>
+        <v>455177</v>
       </c>
       <c r="R44" t="n">
-        <v>6812759</v>
+        <v>6812448</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302744</v>
+        <v>122302585</v>
       </c>
       <c r="B45" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,21 +5077,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455165</v>
+        <v>454995</v>
       </c>
       <c r="R45" t="n">
-        <v>6812443</v>
+        <v>6812454</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122302651</v>
+        <v>122302750</v>
       </c>
       <c r="B46" t="n">
         <v>78656</v>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455119</v>
+        <v>455083</v>
       </c>
       <c r="R46" t="n">
-        <v>6812817</v>
+        <v>6812476</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122302654</v>
+        <v>122302673</v>
       </c>
       <c r="B47" t="n">
         <v>78656</v>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455187</v>
+        <v>455747</v>
       </c>
       <c r="R47" t="n">
-        <v>6812780</v>
+        <v>6812550</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,10 +5367,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302585</v>
+        <v>122302672</v>
       </c>
       <c r="B48" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5383,21 +5383,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454995</v>
+        <v>455638</v>
       </c>
       <c r="R48" t="n">
-        <v>6812454</v>
+        <v>6812544</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5469,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122302773</v>
+        <v>122302746</v>
       </c>
       <c r="B49" t="n">
-        <v>78040</v>
+        <v>78656</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5485,21 +5485,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>454992</v>
+        <v>455138</v>
       </c>
       <c r="R49" t="n">
-        <v>6812487</v>
+        <v>6812473</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,7 +5571,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122302743</v>
+        <v>122302749</v>
       </c>
       <c r="B50" t="n">
         <v>78656</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455165</v>
+        <v>455098</v>
       </c>
       <c r="R50" t="n">
-        <v>6812417</v>
+        <v>6812474</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302537</v>
+        <v>122302751</v>
       </c>
       <c r="B51" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5689,21 +5689,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455203</v>
+        <v>454998</v>
       </c>
       <c r="R51" t="n">
-        <v>6812760</v>
+        <v>6812459</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302668</v>
+        <v>122302579</v>
       </c>
       <c r="B52" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5791,21 +5791,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455485</v>
+        <v>455212</v>
       </c>
       <c r="R52" t="n">
-        <v>6812754</v>
+        <v>6812763</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302671</v>
+        <v>122302585</v>
       </c>
       <c r="B42" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455616</v>
+        <v>454995</v>
       </c>
       <c r="R42" t="n">
-        <v>6812570</v>
+        <v>6812454</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302724</v>
+        <v>122302671</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455449</v>
+        <v>455616</v>
       </c>
       <c r="R43" t="n">
-        <v>6812352</v>
+        <v>6812570</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302594</v>
+        <v>122302724</v>
       </c>
       <c r="B44" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455177</v>
+        <v>455449</v>
       </c>
       <c r="R44" t="n">
-        <v>6812448</v>
+        <v>6812352</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302585</v>
+        <v>122302594</v>
       </c>
       <c r="B45" t="n">
-        <v>78393</v>
+        <v>78392</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,21 +5077,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454995</v>
+        <v>455177</v>
       </c>
       <c r="R45" t="n">
-        <v>6812454</v>
+        <v>6812448</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302753</v>
+        <v>122302659</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454977</v>
+        <v>455293</v>
       </c>
       <c r="R2" t="n">
-        <v>6812451</v>
+        <v>6812728</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302651</v>
+        <v>122302773</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>78040</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455119</v>
+        <v>454992</v>
       </c>
       <c r="R3" t="n">
-        <v>6812817</v>
+        <v>6812487</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302665</v>
+        <v>122302751</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455420</v>
+        <v>454998</v>
       </c>
       <c r="R4" t="n">
-        <v>6812744</v>
+        <v>6812459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302737</v>
+        <v>122302753</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455267</v>
+        <v>454977</v>
       </c>
       <c r="R5" t="n">
-        <v>6812474</v>
+        <v>6812451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302674</v>
+        <v>122302538</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455758</v>
+        <v>455290</v>
       </c>
       <c r="R6" t="n">
-        <v>6812559</v>
+        <v>6812727</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302583</v>
+        <v>122302669</v>
       </c>
       <c r="B7" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455177</v>
+        <v>455567</v>
       </c>
       <c r="R7" t="n">
-        <v>6812448</v>
+        <v>6812725</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302748</v>
+        <v>122302585</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455119</v>
+        <v>454995</v>
       </c>
       <c r="R8" t="n">
-        <v>6812489</v>
+        <v>6812454</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302725</v>
+        <v>122302737</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455413</v>
+        <v>455267</v>
       </c>
       <c r="R9" t="n">
-        <v>6812371</v>
+        <v>6812474</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302726</v>
+        <v>122302604</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455407</v>
+        <v>455405</v>
       </c>
       <c r="R10" t="n">
-        <v>6812392</v>
+        <v>6812359</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302553</v>
+        <v>122302724</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455736</v>
+        <v>455449</v>
       </c>
       <c r="R11" t="n">
-        <v>6812556</v>
+        <v>6812352</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302650</v>
+        <v>122302654</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455089</v>
+        <v>455187</v>
       </c>
       <c r="R12" t="n">
-        <v>6812828</v>
+        <v>6812780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302670</v>
+        <v>122302743</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455615</v>
+        <v>455165</v>
       </c>
       <c r="R13" t="n">
-        <v>6812587</v>
+        <v>6812417</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302754</v>
+        <v>122302748</v>
       </c>
       <c r="B14" t="n">
         <v>78656</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454970</v>
+        <v>455119</v>
       </c>
       <c r="R14" t="n">
-        <v>6812456</v>
+        <v>6812489</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302657</v>
+        <v>122302665</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455243</v>
+        <v>455420</v>
       </c>
       <c r="R15" t="n">
-        <v>6812747</v>
+        <v>6812744</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302659</v>
+        <v>122302749</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455293</v>
+        <v>455098</v>
       </c>
       <c r="R16" t="n">
-        <v>6812728</v>
+        <v>6812474</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302743</v>
+        <v>122302553</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>79245</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455165</v>
+        <v>455736</v>
       </c>
       <c r="R17" t="n">
-        <v>6812417</v>
+        <v>6812556</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302604</v>
+        <v>122302736</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455405</v>
+        <v>455295</v>
       </c>
       <c r="R18" t="n">
-        <v>6812359</v>
+        <v>6812491</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302652</v>
+        <v>122302650</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455165</v>
+        <v>455089</v>
       </c>
       <c r="R19" t="n">
-        <v>6812792</v>
+        <v>6812828</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302653</v>
+        <v>122302672</v>
       </c>
       <c r="B20" t="n">
         <v>78656</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455173</v>
+        <v>455638</v>
       </c>
       <c r="R20" t="n">
-        <v>6812786</v>
+        <v>6812544</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302655</v>
+        <v>122302653</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455201</v>
+        <v>455173</v>
       </c>
       <c r="R21" t="n">
-        <v>6812767</v>
+        <v>6812786</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302584</v>
+        <v>122302745</v>
       </c>
       <c r="B23" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455165</v>
+        <v>455154</v>
       </c>
       <c r="R23" t="n">
-        <v>6812417</v>
+        <v>6812449</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302745</v>
+        <v>122302583</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455154</v>
+        <v>455177</v>
       </c>
       <c r="R24" t="n">
-        <v>6812449</v>
+        <v>6812448</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302656</v>
+        <v>122302658</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455229</v>
+        <v>455259</v>
       </c>
       <c r="R25" t="n">
-        <v>6812759</v>
+        <v>6812731</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302669</v>
+        <v>122302552</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455567</v>
+        <v>455409</v>
       </c>
       <c r="R26" t="n">
-        <v>6812725</v>
+        <v>6812375</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3225,7 +3225,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302667</v>
+        <v>122302727</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455438</v>
+        <v>455408</v>
       </c>
       <c r="R27" t="n">
-        <v>6812744</v>
+        <v>6812407</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302773</v>
+        <v>122302747</v>
       </c>
       <c r="B28" t="n">
-        <v>78040</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454992</v>
+        <v>455137</v>
       </c>
       <c r="R28" t="n">
-        <v>6812487</v>
+        <v>6812474</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,7 +3429,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122302752</v>
+        <v>122302657</v>
       </c>
       <c r="B29" t="n">
         <v>78656</v>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454985</v>
+        <v>455243</v>
       </c>
       <c r="R29" t="n">
-        <v>6812455</v>
+        <v>6812747</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302658</v>
+        <v>122302652</v>
       </c>
       <c r="B30" t="n">
         <v>78656</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455259</v>
+        <v>455165</v>
       </c>
       <c r="R30" t="n">
-        <v>6812731</v>
+        <v>6812792</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302747</v>
+        <v>122302594</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>78392</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455137</v>
+        <v>455177</v>
       </c>
       <c r="R31" t="n">
-        <v>6812474</v>
+        <v>6812448</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302727</v>
+        <v>122302668</v>
       </c>
       <c r="B32" t="n">
         <v>78656</v>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455408</v>
+        <v>455485</v>
       </c>
       <c r="R32" t="n">
-        <v>6812407</v>
+        <v>6812754</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -3837,7 +3837,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122302666</v>
+        <v>122302656</v>
       </c>
       <c r="B33" t="n">
         <v>78656</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455428</v>
+        <v>455229</v>
       </c>
       <c r="R33" t="n">
-        <v>6812747</v>
+        <v>6812759</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122302736</v>
+        <v>122302754</v>
       </c>
       <c r="B34" t="n">
         <v>78656</v>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455295</v>
+        <v>454970</v>
       </c>
       <c r="R34" t="n">
-        <v>6812491</v>
+        <v>6812456</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122302668</v>
+        <v>122302603</v>
       </c>
       <c r="B35" t="n">
         <v>78656</v>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455485</v>
+        <v>455413</v>
       </c>
       <c r="R35" t="n">
-        <v>6812754</v>
+        <v>6812351</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4143,7 +4143,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122302605</v>
+        <v>122302666</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455043</v>
+        <v>455428</v>
       </c>
       <c r="R36" t="n">
-        <v>6812499</v>
+        <v>6812747</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302654</v>
+        <v>122302651</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455187</v>
+        <v>455119</v>
       </c>
       <c r="R37" t="n">
-        <v>6812780</v>
+        <v>6812817</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4449,7 +4449,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302603</v>
+        <v>122302673</v>
       </c>
       <c r="B39" t="n">
         <v>78656</v>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455413</v>
+        <v>455747</v>
       </c>
       <c r="R39" t="n">
-        <v>6812351</v>
+        <v>6812550</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122302538</v>
+        <v>122302667</v>
       </c>
       <c r="B40" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455290</v>
+        <v>455438</v>
       </c>
       <c r="R40" t="n">
-        <v>6812727</v>
+        <v>6812744</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302552</v>
+        <v>122302671</v>
       </c>
       <c r="B41" t="n">
-        <v>78690</v>
+        <v>78656</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455409</v>
+        <v>455616</v>
       </c>
       <c r="R41" t="n">
-        <v>6812375</v>
+        <v>6812570</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4755,7 +4755,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302585</v>
+        <v>122302579</v>
       </c>
       <c r="B42" t="n">
         <v>78393</v>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454995</v>
+        <v>455212</v>
       </c>
       <c r="R42" t="n">
-        <v>6812454</v>
+        <v>6812763</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302671</v>
+        <v>122302605</v>
       </c>
       <c r="B43" t="n">
         <v>78656</v>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455616</v>
+        <v>455043</v>
       </c>
       <c r="R43" t="n">
-        <v>6812570</v>
+        <v>6812499</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302724</v>
+        <v>122302674</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455449</v>
+        <v>455758</v>
       </c>
       <c r="R44" t="n">
-        <v>6812352</v>
+        <v>6812559</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302594</v>
+        <v>122302725</v>
       </c>
       <c r="B45" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,21 +5077,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455177</v>
+        <v>455413</v>
       </c>
       <c r="R45" t="n">
-        <v>6812448</v>
+        <v>6812371</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5163,7 +5163,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122302750</v>
+        <v>122302726</v>
       </c>
       <c r="B46" t="n">
         <v>78656</v>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455083</v>
+        <v>455407</v>
       </c>
       <c r="R46" t="n">
-        <v>6812476</v>
+        <v>6812392</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5265,7 +5265,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122302673</v>
+        <v>122302655</v>
       </c>
       <c r="B47" t="n">
         <v>78656</v>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455747</v>
+        <v>455201</v>
       </c>
       <c r="R47" t="n">
-        <v>6812550</v>
+        <v>6812767</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,7 +5367,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302672</v>
+        <v>122302752</v>
       </c>
       <c r="B48" t="n">
         <v>78656</v>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455638</v>
+        <v>454985</v>
       </c>
       <c r="R48" t="n">
-        <v>6812544</v>
+        <v>6812455</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5571,7 +5571,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122302749</v>
+        <v>122302750</v>
       </c>
       <c r="B50" t="n">
         <v>78656</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455098</v>
+        <v>455083</v>
       </c>
       <c r="R50" t="n">
-        <v>6812474</v>
+        <v>6812476</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,7 +5673,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302751</v>
+        <v>122302670</v>
       </c>
       <c r="B51" t="n">
         <v>78656</v>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>454998</v>
+        <v>455615</v>
       </c>
       <c r="R51" t="n">
-        <v>6812459</v>
+        <v>6812587</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,7 +5775,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302579</v>
+        <v>122302584</v>
       </c>
       <c r="B52" t="n">
         <v>78393</v>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455212</v>
+        <v>455165</v>
       </c>
       <c r="R52" t="n">
-        <v>6812763</v>
+        <v>6812417</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302659</v>
+        <v>122302666</v>
       </c>
       <c r="B2" t="n">
         <v>78656</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455293</v>
+        <v>455428</v>
       </c>
       <c r="R2" t="n">
-        <v>6812728</v>
+        <v>6812747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302773</v>
+        <v>122302654</v>
       </c>
       <c r="B3" t="n">
-        <v>78040</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454992</v>
+        <v>455187</v>
       </c>
       <c r="R3" t="n">
-        <v>6812487</v>
+        <v>6812780</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302751</v>
+        <v>122302744</v>
       </c>
       <c r="B4" t="n">
         <v>78656</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454998</v>
+        <v>455165</v>
       </c>
       <c r="R4" t="n">
-        <v>6812459</v>
+        <v>6812443</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302753</v>
+        <v>122302727</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454977</v>
+        <v>455408</v>
       </c>
       <c r="R5" t="n">
-        <v>6812451</v>
+        <v>6812407</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302538</v>
+        <v>122302579</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>78393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455290</v>
+        <v>455212</v>
       </c>
       <c r="R6" t="n">
-        <v>6812727</v>
+        <v>6812763</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302669</v>
+        <v>122302584</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455567</v>
+        <v>455165</v>
       </c>
       <c r="R7" t="n">
-        <v>6812725</v>
+        <v>6812417</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302585</v>
+        <v>122302726</v>
       </c>
       <c r="B8" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454995</v>
+        <v>455407</v>
       </c>
       <c r="R8" t="n">
-        <v>6812454</v>
+        <v>6812392</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302737</v>
+        <v>122302736</v>
       </c>
       <c r="B9" t="n">
         <v>78656</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455267</v>
+        <v>455295</v>
       </c>
       <c r="R9" t="n">
-        <v>6812474</v>
+        <v>6812491</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302604</v>
+        <v>122302749</v>
       </c>
       <c r="B10" t="n">
         <v>78656</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455405</v>
+        <v>455098</v>
       </c>
       <c r="R10" t="n">
-        <v>6812359</v>
+        <v>6812474</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302724</v>
+        <v>122302585</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455449</v>
+        <v>454995</v>
       </c>
       <c r="R11" t="n">
-        <v>6812352</v>
+        <v>6812454</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302654</v>
+        <v>122302604</v>
       </c>
       <c r="B12" t="n">
         <v>78656</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455187</v>
+        <v>455405</v>
       </c>
       <c r="R12" t="n">
-        <v>6812780</v>
+        <v>6812359</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302743</v>
+        <v>122302737</v>
       </c>
       <c r="B13" t="n">
         <v>78656</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455165</v>
+        <v>455267</v>
       </c>
       <c r="R13" t="n">
-        <v>6812417</v>
+        <v>6812474</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302748</v>
+        <v>122302725</v>
       </c>
       <c r="B14" t="n">
         <v>78656</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455119</v>
+        <v>455413</v>
       </c>
       <c r="R14" t="n">
-        <v>6812489</v>
+        <v>6812371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302665</v>
+        <v>122302674</v>
       </c>
       <c r="B15" t="n">
         <v>78656</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455420</v>
+        <v>455758</v>
       </c>
       <c r="R15" t="n">
-        <v>6812744</v>
+        <v>6812559</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302749</v>
+        <v>122302651</v>
       </c>
       <c r="B16" t="n">
         <v>78656</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455098</v>
+        <v>455119</v>
       </c>
       <c r="R16" t="n">
-        <v>6812474</v>
+        <v>6812817</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302553</v>
+        <v>122302653</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455736</v>
+        <v>455173</v>
       </c>
       <c r="R17" t="n">
-        <v>6812556</v>
+        <v>6812786</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302736</v>
+        <v>122302650</v>
       </c>
       <c r="B18" t="n">
         <v>78656</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455295</v>
+        <v>455089</v>
       </c>
       <c r="R18" t="n">
-        <v>6812491</v>
+        <v>6812828</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302650</v>
+        <v>122302743</v>
       </c>
       <c r="B19" t="n">
         <v>78656</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455089</v>
+        <v>455165</v>
       </c>
       <c r="R19" t="n">
-        <v>6812828</v>
+        <v>6812417</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302653</v>
+        <v>122302752</v>
       </c>
       <c r="B21" t="n">
         <v>78656</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455173</v>
+        <v>454985</v>
       </c>
       <c r="R21" t="n">
-        <v>6812786</v>
+        <v>6812455</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302744</v>
+        <v>122302665</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455165</v>
+        <v>455420</v>
       </c>
       <c r="R22" t="n">
-        <v>6812443</v>
+        <v>6812744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302745</v>
+        <v>122302537</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455154</v>
+        <v>455203</v>
       </c>
       <c r="R23" t="n">
-        <v>6812449</v>
+        <v>6812760</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302583</v>
+        <v>122302668</v>
       </c>
       <c r="B24" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455177</v>
+        <v>455485</v>
       </c>
       <c r="R24" t="n">
-        <v>6812448</v>
+        <v>6812754</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302658</v>
+        <v>122302673</v>
       </c>
       <c r="B25" t="n">
         <v>78656</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455259</v>
+        <v>455747</v>
       </c>
       <c r="R25" t="n">
-        <v>6812731</v>
+        <v>6812550</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302552</v>
+        <v>122302553</v>
       </c>
       <c r="B26" t="n">
-        <v>78690</v>
+        <v>79245</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455409</v>
+        <v>455736</v>
       </c>
       <c r="R26" t="n">
-        <v>6812375</v>
+        <v>6812556</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3225,7 +3225,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302727</v>
+        <v>122302670</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455408</v>
+        <v>455615</v>
       </c>
       <c r="R27" t="n">
-        <v>6812407</v>
+        <v>6812587</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302747</v>
+        <v>122302538</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>79274</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455137</v>
+        <v>455290</v>
       </c>
       <c r="R28" t="n">
-        <v>6812474</v>
+        <v>6812727</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302652</v>
+        <v>122302751</v>
       </c>
       <c r="B30" t="n">
         <v>78656</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455165</v>
+        <v>454998</v>
       </c>
       <c r="R30" t="n">
-        <v>6812792</v>
+        <v>6812459</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302594</v>
+        <v>122302656</v>
       </c>
       <c r="B31" t="n">
-        <v>78392</v>
+        <v>78656</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455177</v>
+        <v>455229</v>
       </c>
       <c r="R31" t="n">
-        <v>6812448</v>
+        <v>6812759</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302668</v>
+        <v>122302748</v>
       </c>
       <c r="B32" t="n">
         <v>78656</v>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455485</v>
+        <v>455119</v>
       </c>
       <c r="R32" t="n">
-        <v>6812754</v>
+        <v>6812489</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122302656</v>
+        <v>122302658</v>
       </c>
       <c r="B33" t="n">
         <v>78656</v>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455229</v>
+        <v>455259</v>
       </c>
       <c r="R33" t="n">
-        <v>6812759</v>
+        <v>6812731</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122302754</v>
+        <v>122302605</v>
       </c>
       <c r="B34" t="n">
         <v>78656</v>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454970</v>
+        <v>455043</v>
       </c>
       <c r="R34" t="n">
-        <v>6812456</v>
+        <v>6812499</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122302603</v>
+        <v>122302671</v>
       </c>
       <c r="B35" t="n">
         <v>78656</v>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455413</v>
+        <v>455616</v>
       </c>
       <c r="R35" t="n">
-        <v>6812351</v>
+        <v>6812570</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4143,7 +4143,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122302666</v>
+        <v>122302746</v>
       </c>
       <c r="B36" t="n">
         <v>78656</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455428</v>
+        <v>455138</v>
       </c>
       <c r="R36" t="n">
-        <v>6812747</v>
+        <v>6812473</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302651</v>
+        <v>122302659</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455119</v>
+        <v>455293</v>
       </c>
       <c r="R37" t="n">
-        <v>6812817</v>
+        <v>6812728</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302537</v>
+        <v>122302667</v>
       </c>
       <c r="B38" t="n">
-        <v>79274</v>
+        <v>78656</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4363,21 +4363,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455203</v>
+        <v>455438</v>
       </c>
       <c r="R38" t="n">
-        <v>6812760</v>
+        <v>6812744</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302673</v>
+        <v>122302583</v>
       </c>
       <c r="B39" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455747</v>
+        <v>455177</v>
       </c>
       <c r="R39" t="n">
-        <v>6812550</v>
+        <v>6812448</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122302667</v>
+        <v>122302552</v>
       </c>
       <c r="B40" t="n">
-        <v>78656</v>
+        <v>78690</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455438</v>
+        <v>455409</v>
       </c>
       <c r="R40" t="n">
-        <v>6812744</v>
+        <v>6812375</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4653,7 +4653,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302671</v>
+        <v>122302724</v>
       </c>
       <c r="B41" t="n">
         <v>78656</v>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455616</v>
+        <v>455449</v>
       </c>
       <c r="R41" t="n">
-        <v>6812570</v>
+        <v>6812352</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302579</v>
+        <v>122302773</v>
       </c>
       <c r="B42" t="n">
-        <v>78393</v>
+        <v>78040</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455212</v>
+        <v>454992</v>
       </c>
       <c r="R42" t="n">
-        <v>6812763</v>
+        <v>6812487</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302605</v>
+        <v>122302594</v>
       </c>
       <c r="B43" t="n">
-        <v>78656</v>
+        <v>78392</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455043</v>
+        <v>455177</v>
       </c>
       <c r="R43" t="n">
-        <v>6812499</v>
+        <v>6812448</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302674</v>
+        <v>122302754</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455758</v>
+        <v>454970</v>
       </c>
       <c r="R44" t="n">
-        <v>6812559</v>
+        <v>6812456</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,7 +5061,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302725</v>
+        <v>122302753</v>
       </c>
       <c r="B45" t="n">
         <v>78656</v>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455413</v>
+        <v>454977</v>
       </c>
       <c r="R45" t="n">
-        <v>6812371</v>
+        <v>6812451</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5163,7 +5163,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122302726</v>
+        <v>122302747</v>
       </c>
       <c r="B46" t="n">
         <v>78656</v>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455407</v>
+        <v>455137</v>
       </c>
       <c r="R46" t="n">
-        <v>6812392</v>
+        <v>6812474</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -5367,7 +5367,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302752</v>
+        <v>122302750</v>
       </c>
       <c r="B48" t="n">
         <v>78656</v>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>454985</v>
+        <v>455083</v>
       </c>
       <c r="R48" t="n">
-        <v>6812455</v>
+        <v>6812476</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122302746</v>
+        <v>122302669</v>
       </c>
       <c r="B49" t="n">
         <v>78656</v>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455138</v>
+        <v>455567</v>
       </c>
       <c r="R49" t="n">
-        <v>6812473</v>
+        <v>6812725</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,7 +5571,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122302750</v>
+        <v>122302652</v>
       </c>
       <c r="B50" t="n">
         <v>78656</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455083</v>
+        <v>455165</v>
       </c>
       <c r="R50" t="n">
-        <v>6812476</v>
+        <v>6812792</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,7 +5673,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302670</v>
+        <v>122302745</v>
       </c>
       <c r="B51" t="n">
         <v>78656</v>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455615</v>
+        <v>455154</v>
       </c>
       <c r="R51" t="n">
-        <v>6812587</v>
+        <v>6812449</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302584</v>
+        <v>122302603</v>
       </c>
       <c r="B52" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5791,21 +5791,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455165</v>
+        <v>455413</v>
       </c>
       <c r="R52" t="n">
-        <v>6812417</v>
+        <v>6812351</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302666</v>
+        <v>122302672</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455428</v>
+        <v>455638</v>
       </c>
       <c r="R2" t="n">
-        <v>6812747</v>
+        <v>6812544</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302654</v>
+        <v>122302652</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455187</v>
+        <v>455165</v>
       </c>
       <c r="R3" t="n">
-        <v>6812780</v>
+        <v>6812792</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302744</v>
+        <v>122302668</v>
       </c>
       <c r="B4" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455165</v>
+        <v>455485</v>
       </c>
       <c r="R4" t="n">
-        <v>6812443</v>
+        <v>6812754</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302727</v>
+        <v>122302654</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455408</v>
+        <v>455187</v>
       </c>
       <c r="R5" t="n">
-        <v>6812407</v>
+        <v>6812780</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302579</v>
+        <v>122302754</v>
       </c>
       <c r="B6" t="n">
-        <v>78393</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455212</v>
+        <v>454970</v>
       </c>
       <c r="R6" t="n">
-        <v>6812763</v>
+        <v>6812456</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302584</v>
+        <v>122302667</v>
       </c>
       <c r="B7" t="n">
-        <v>78393</v>
+        <v>78657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455165</v>
+        <v>455438</v>
       </c>
       <c r="R7" t="n">
-        <v>6812417</v>
+        <v>6812744</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302726</v>
+        <v>122302725</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455407</v>
+        <v>455413</v>
       </c>
       <c r="R8" t="n">
-        <v>6812392</v>
+        <v>6812371</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302736</v>
+        <v>122302605</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455295</v>
+        <v>455043</v>
       </c>
       <c r="R9" t="n">
-        <v>6812491</v>
+        <v>6812499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302749</v>
+        <v>122302666</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455098</v>
+        <v>455428</v>
       </c>
       <c r="R10" t="n">
-        <v>6812474</v>
+        <v>6812747</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302585</v>
+        <v>122302744</v>
       </c>
       <c r="B11" t="n">
-        <v>78393</v>
+        <v>78657</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454995</v>
+        <v>455165</v>
       </c>
       <c r="R11" t="n">
-        <v>6812454</v>
+        <v>6812443</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302604</v>
+        <v>122302665</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455405</v>
+        <v>455420</v>
       </c>
       <c r="R12" t="n">
-        <v>6812359</v>
+        <v>6812744</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302737</v>
+        <v>122302669</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455267</v>
+        <v>455567</v>
       </c>
       <c r="R13" t="n">
-        <v>6812474</v>
+        <v>6812725</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302725</v>
+        <v>122302747</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455413</v>
+        <v>455137</v>
       </c>
       <c r="R14" t="n">
-        <v>6812371</v>
+        <v>6812474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302674</v>
+        <v>122302653</v>
       </c>
       <c r="B15" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455758</v>
+        <v>455173</v>
       </c>
       <c r="R15" t="n">
-        <v>6812559</v>
+        <v>6812786</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302651</v>
+        <v>122302748</v>
       </c>
       <c r="B16" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>455119</v>
       </c>
       <c r="R16" t="n">
-        <v>6812817</v>
+        <v>6812489</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302653</v>
+        <v>122302656</v>
       </c>
       <c r="B17" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455173</v>
+        <v>455229</v>
       </c>
       <c r="R17" t="n">
-        <v>6812786</v>
+        <v>6812759</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302650</v>
+        <v>122302727</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455089</v>
+        <v>455408</v>
       </c>
       <c r="R18" t="n">
-        <v>6812828</v>
+        <v>6812407</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302743</v>
+        <v>122302673</v>
       </c>
       <c r="B19" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455165</v>
+        <v>455747</v>
       </c>
       <c r="R19" t="n">
-        <v>6812417</v>
+        <v>6812550</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302672</v>
+        <v>122302583</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>78394</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455638</v>
+        <v>455177</v>
       </c>
       <c r="R20" t="n">
-        <v>6812544</v>
+        <v>6812448</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302752</v>
+        <v>122302773</v>
       </c>
       <c r="B21" t="n">
-        <v>78656</v>
+        <v>78041</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454985</v>
+        <v>454992</v>
       </c>
       <c r="R21" t="n">
-        <v>6812455</v>
+        <v>6812487</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302665</v>
+        <v>122302594</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>78393</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455420</v>
+        <v>455177</v>
       </c>
       <c r="R22" t="n">
-        <v>6812744</v>
+        <v>6812448</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302537</v>
+        <v>122302579</v>
       </c>
       <c r="B23" t="n">
-        <v>79274</v>
+        <v>78394</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455203</v>
+        <v>455212</v>
       </c>
       <c r="R23" t="n">
-        <v>6812760</v>
+        <v>6812763</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302668</v>
+        <v>122302746</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455485</v>
+        <v>455138</v>
       </c>
       <c r="R24" t="n">
-        <v>6812754</v>
+        <v>6812473</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302673</v>
+        <v>122302604</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455747</v>
+        <v>455405</v>
       </c>
       <c r="R25" t="n">
-        <v>6812550</v>
+        <v>6812359</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302553</v>
+        <v>122302538</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>79275</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455736</v>
+        <v>455290</v>
       </c>
       <c r="R26" t="n">
-        <v>6812556</v>
+        <v>6812727</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302670</v>
+        <v>122302736</v>
       </c>
       <c r="B27" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455615</v>
+        <v>455295</v>
       </c>
       <c r="R27" t="n">
-        <v>6812587</v>
+        <v>6812491</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302538</v>
+        <v>122302657</v>
       </c>
       <c r="B28" t="n">
-        <v>79274</v>
+        <v>78657</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455290</v>
+        <v>455243</v>
       </c>
       <c r="R28" t="n">
-        <v>6812727</v>
+        <v>6812747</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122302657</v>
+        <v>122302603</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455243</v>
+        <v>455413</v>
       </c>
       <c r="R29" t="n">
-        <v>6812747</v>
+        <v>6812351</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302751</v>
+        <v>122302750</v>
       </c>
       <c r="B30" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454998</v>
+        <v>455083</v>
       </c>
       <c r="R30" t="n">
-        <v>6812459</v>
+        <v>6812476</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302656</v>
+        <v>122302658</v>
       </c>
       <c r="B31" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455229</v>
+        <v>455259</v>
       </c>
       <c r="R31" t="n">
-        <v>6812759</v>
+        <v>6812731</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302748</v>
+        <v>122302585</v>
       </c>
       <c r="B32" t="n">
-        <v>78656</v>
+        <v>78394</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455119</v>
+        <v>454995</v>
       </c>
       <c r="R32" t="n">
-        <v>6812489</v>
+        <v>6812454</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122302658</v>
+        <v>122302749</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455259</v>
+        <v>455098</v>
       </c>
       <c r="R33" t="n">
-        <v>6812731</v>
+        <v>6812474</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122302605</v>
+        <v>122302659</v>
       </c>
       <c r="B34" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455043</v>
+        <v>455293</v>
       </c>
       <c r="R34" t="n">
-        <v>6812499</v>
+        <v>6812728</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122302671</v>
+        <v>122302751</v>
       </c>
       <c r="B35" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455616</v>
+        <v>454998</v>
       </c>
       <c r="R35" t="n">
-        <v>6812570</v>
+        <v>6812459</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122302746</v>
+        <v>122302674</v>
       </c>
       <c r="B36" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455138</v>
+        <v>455758</v>
       </c>
       <c r="R36" t="n">
-        <v>6812473</v>
+        <v>6812559</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302659</v>
+        <v>122302752</v>
       </c>
       <c r="B37" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455293</v>
+        <v>454985</v>
       </c>
       <c r="R37" t="n">
-        <v>6812728</v>
+        <v>6812455</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302667</v>
+        <v>122302655</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455438</v>
+        <v>455201</v>
       </c>
       <c r="R38" t="n">
-        <v>6812744</v>
+        <v>6812767</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302583</v>
+        <v>122302753</v>
       </c>
       <c r="B39" t="n">
-        <v>78393</v>
+        <v>78657</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,21 +4465,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455177</v>
+        <v>454977</v>
       </c>
       <c r="R39" t="n">
-        <v>6812448</v>
+        <v>6812451</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122302552</v>
+        <v>122302537</v>
       </c>
       <c r="B40" t="n">
-        <v>78690</v>
+        <v>79275</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455409</v>
+        <v>455203</v>
       </c>
       <c r="R40" t="n">
-        <v>6812375</v>
+        <v>6812760</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302724</v>
+        <v>122302671</v>
       </c>
       <c r="B41" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455449</v>
+        <v>455616</v>
       </c>
       <c r="R41" t="n">
-        <v>6812352</v>
+        <v>6812570</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302773</v>
+        <v>122302724</v>
       </c>
       <c r="B42" t="n">
-        <v>78040</v>
+        <v>78657</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454992</v>
+        <v>455449</v>
       </c>
       <c r="R42" t="n">
-        <v>6812487</v>
+        <v>6812352</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -4857,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302594</v>
+        <v>122302726</v>
       </c>
       <c r="B43" t="n">
-        <v>78392</v>
+        <v>78657</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455177</v>
+        <v>455407</v>
       </c>
       <c r="R43" t="n">
-        <v>6812448</v>
+        <v>6812392</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302754</v>
+        <v>122302552</v>
       </c>
       <c r="B44" t="n">
-        <v>78656</v>
+        <v>78691</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>454970</v>
+        <v>455409</v>
       </c>
       <c r="R44" t="n">
-        <v>6812456</v>
+        <v>6812375</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302753</v>
+        <v>122302670</v>
       </c>
       <c r="B45" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>454977</v>
+        <v>455615</v>
       </c>
       <c r="R45" t="n">
-        <v>6812451</v>
+        <v>6812587</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122302747</v>
+        <v>122302737</v>
       </c>
       <c r="B46" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455137</v>
+        <v>455267</v>
       </c>
       <c r="R46" t="n">
         <v>6812474</v>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122302655</v>
+        <v>122302745</v>
       </c>
       <c r="B47" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455201</v>
+        <v>455154</v>
       </c>
       <c r="R47" t="n">
-        <v>6812767</v>
+        <v>6812449</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,10 +5367,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302750</v>
+        <v>122302651</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455083</v>
+        <v>455119</v>
       </c>
       <c r="R48" t="n">
-        <v>6812476</v>
+        <v>6812817</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5469,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122302669</v>
+        <v>122302584</v>
       </c>
       <c r="B49" t="n">
-        <v>78656</v>
+        <v>78394</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5485,21 +5485,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455567</v>
+        <v>455165</v>
       </c>
       <c r="R49" t="n">
-        <v>6812725</v>
+        <v>6812417</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,10 +5571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122302652</v>
+        <v>122302650</v>
       </c>
       <c r="B50" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455165</v>
+        <v>455089</v>
       </c>
       <c r="R50" t="n">
-        <v>6812792</v>
+        <v>6812828</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302745</v>
+        <v>122302553</v>
       </c>
       <c r="B51" t="n">
-        <v>78656</v>
+        <v>79246</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5689,21 +5689,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455154</v>
+        <v>455736</v>
       </c>
       <c r="R51" t="n">
-        <v>6812449</v>
+        <v>6812556</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302603</v>
+        <v>122302743</v>
       </c>
       <c r="B52" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455413</v>
+        <v>455165</v>
       </c>
       <c r="R52" t="n">
-        <v>6812351</v>
+        <v>6812417</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122302603</v>
+        <v>122302585</v>
       </c>
       <c r="B29" t="n">
-        <v>78657</v>
+        <v>78394</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455413</v>
+        <v>454995</v>
       </c>
       <c r="R29" t="n">
-        <v>6812351</v>
+        <v>6812454</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3531,7 +3531,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302750</v>
+        <v>122302603</v>
       </c>
       <c r="B30" t="n">
         <v>78657</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455083</v>
+        <v>455413</v>
       </c>
       <c r="R30" t="n">
-        <v>6812476</v>
+        <v>6812351</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3633,7 +3633,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302658</v>
+        <v>122302750</v>
       </c>
       <c r="B31" t="n">
         <v>78657</v>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455259</v>
+        <v>455083</v>
       </c>
       <c r="R31" t="n">
-        <v>6812731</v>
+        <v>6812476</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302585</v>
+        <v>122302658</v>
       </c>
       <c r="B32" t="n">
-        <v>78394</v>
+        <v>78657</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454995</v>
+        <v>455259</v>
       </c>
       <c r="R32" t="n">
-        <v>6812454</v>
+        <v>6812731</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122302745</v>
+        <v>122302584</v>
       </c>
       <c r="B47" t="n">
-        <v>78657</v>
+        <v>78394</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5281,21 +5281,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455154</v>
+        <v>455165</v>
       </c>
       <c r="R47" t="n">
-        <v>6812449</v>
+        <v>6812417</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,7 +5367,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302651</v>
+        <v>122302745</v>
       </c>
       <c r="B48" t="n">
         <v>78657</v>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455119</v>
+        <v>455154</v>
       </c>
       <c r="R48" t="n">
-        <v>6812817</v>
+        <v>6812449</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5469,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122302584</v>
+        <v>122302651</v>
       </c>
       <c r="B49" t="n">
-        <v>78394</v>
+        <v>78657</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5485,21 +5485,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455165</v>
+        <v>455119</v>
       </c>
       <c r="R49" t="n">
-        <v>6812417</v>
+        <v>6812817</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302553</v>
+        <v>122302743</v>
       </c>
       <c r="B51" t="n">
-        <v>79246</v>
+        <v>78657</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5689,21 +5689,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455736</v>
+        <v>455165</v>
       </c>
       <c r="R51" t="n">
-        <v>6812556</v>
+        <v>6812417</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302743</v>
+        <v>122302553</v>
       </c>
       <c r="B52" t="n">
-        <v>78657</v>
+        <v>79246</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5791,21 +5791,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455165</v>
+        <v>455736</v>
       </c>
       <c r="R52" t="n">
-        <v>6812417</v>
+        <v>6812556</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302672</v>
+        <v>122302736</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455638</v>
+        <v>455295</v>
       </c>
       <c r="R2" t="n">
-        <v>6812544</v>
+        <v>6812491</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302652</v>
+        <v>122302745</v>
       </c>
       <c r="B3" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455165</v>
+        <v>455154</v>
       </c>
       <c r="R3" t="n">
-        <v>6812792</v>
+        <v>6812449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302668</v>
+        <v>122302752</v>
       </c>
       <c r="B4" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455485</v>
+        <v>454985</v>
       </c>
       <c r="R4" t="n">
-        <v>6812754</v>
+        <v>6812455</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302654</v>
+        <v>122302658</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455187</v>
+        <v>455259</v>
       </c>
       <c r="R5" t="n">
-        <v>6812780</v>
+        <v>6812731</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302754</v>
+        <v>122302674</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454970</v>
+        <v>455758</v>
       </c>
       <c r="R6" t="n">
-        <v>6812456</v>
+        <v>6812559</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302667</v>
+        <v>122302553</v>
       </c>
       <c r="B7" t="n">
-        <v>78657</v>
+        <v>79249</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455438</v>
+        <v>455736</v>
       </c>
       <c r="R7" t="n">
-        <v>6812744</v>
+        <v>6812556</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302725</v>
+        <v>122302671</v>
       </c>
       <c r="B8" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455413</v>
+        <v>455616</v>
       </c>
       <c r="R8" t="n">
-        <v>6812371</v>
+        <v>6812570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302605</v>
+        <v>122302751</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455043</v>
+        <v>454998</v>
       </c>
       <c r="R9" t="n">
-        <v>6812499</v>
+        <v>6812459</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302666</v>
+        <v>122302552</v>
       </c>
       <c r="B10" t="n">
-        <v>78657</v>
+        <v>78694</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455428</v>
+        <v>455409</v>
       </c>
       <c r="R10" t="n">
-        <v>6812747</v>
+        <v>6812375</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302744</v>
+        <v>122302651</v>
       </c>
       <c r="B11" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455165</v>
+        <v>455119</v>
       </c>
       <c r="R11" t="n">
-        <v>6812443</v>
+        <v>6812817</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302665</v>
+        <v>122302655</v>
       </c>
       <c r="B12" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455420</v>
+        <v>455201</v>
       </c>
       <c r="R12" t="n">
-        <v>6812744</v>
+        <v>6812767</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302669</v>
+        <v>122302665</v>
       </c>
       <c r="B13" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455567</v>
+        <v>455420</v>
       </c>
       <c r="R13" t="n">
-        <v>6812725</v>
+        <v>6812744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302747</v>
+        <v>122302727</v>
       </c>
       <c r="B14" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455137</v>
+        <v>455408</v>
       </c>
       <c r="R14" t="n">
-        <v>6812474</v>
+        <v>6812407</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122302653</v>
+        <v>122302670</v>
       </c>
       <c r="B15" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455173</v>
+        <v>455615</v>
       </c>
       <c r="R15" t="n">
-        <v>6812786</v>
+        <v>6812587</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302748</v>
+        <v>122302747</v>
       </c>
       <c r="B16" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455119</v>
+        <v>455137</v>
       </c>
       <c r="R16" t="n">
-        <v>6812489</v>
+        <v>6812474</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302656</v>
+        <v>122302673</v>
       </c>
       <c r="B17" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455229</v>
+        <v>455747</v>
       </c>
       <c r="R17" t="n">
-        <v>6812759</v>
+        <v>6812550</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302727</v>
+        <v>122302603</v>
       </c>
       <c r="B18" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455408</v>
+        <v>455413</v>
       </c>
       <c r="R18" t="n">
-        <v>6812407</v>
+        <v>6812351</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302673</v>
+        <v>122302725</v>
       </c>
       <c r="B19" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455747</v>
+        <v>455413</v>
       </c>
       <c r="R19" t="n">
-        <v>6812550</v>
+        <v>6812371</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302583</v>
+        <v>122302585</v>
       </c>
       <c r="B20" t="n">
-        <v>78394</v>
+        <v>78397</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455177</v>
+        <v>454995</v>
       </c>
       <c r="R20" t="n">
-        <v>6812448</v>
+        <v>6812454</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302773</v>
+        <v>122302748</v>
       </c>
       <c r="B21" t="n">
-        <v>78041</v>
+        <v>78660</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454992</v>
+        <v>455119</v>
       </c>
       <c r="R21" t="n">
-        <v>6812487</v>
+        <v>6812489</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302594</v>
+        <v>122302668</v>
       </c>
       <c r="B22" t="n">
-        <v>78393</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455177</v>
+        <v>455485</v>
       </c>
       <c r="R22" t="n">
-        <v>6812448</v>
+        <v>6812754</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302579</v>
+        <v>122302667</v>
       </c>
       <c r="B23" t="n">
-        <v>78394</v>
+        <v>78660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455212</v>
+        <v>455438</v>
       </c>
       <c r="R23" t="n">
-        <v>6812763</v>
+        <v>6812744</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302746</v>
+        <v>122302594</v>
       </c>
       <c r="B24" t="n">
-        <v>78657</v>
+        <v>78396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455138</v>
+        <v>455177</v>
       </c>
       <c r="R24" t="n">
-        <v>6812473</v>
+        <v>6812448</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302604</v>
+        <v>122302746</v>
       </c>
       <c r="B25" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455405</v>
+        <v>455138</v>
       </c>
       <c r="R25" t="n">
-        <v>6812359</v>
+        <v>6812473</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3123,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302538</v>
+        <v>122302605</v>
       </c>
       <c r="B26" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455290</v>
+        <v>455043</v>
       </c>
       <c r="R26" t="n">
-        <v>6812727</v>
+        <v>6812499</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302736</v>
+        <v>122302754</v>
       </c>
       <c r="B27" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455295</v>
+        <v>454970</v>
       </c>
       <c r="R27" t="n">
-        <v>6812491</v>
+        <v>6812456</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302657</v>
+        <v>122302537</v>
       </c>
       <c r="B28" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455243</v>
+        <v>455203</v>
       </c>
       <c r="R28" t="n">
-        <v>6812747</v>
+        <v>6812760</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122302585</v>
+        <v>122302579</v>
       </c>
       <c r="B29" t="n">
-        <v>78394</v>
+        <v>78397</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454995</v>
+        <v>455212</v>
       </c>
       <c r="R29" t="n">
-        <v>6812454</v>
+        <v>6812763</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302603</v>
+        <v>122302656</v>
       </c>
       <c r="B30" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455413</v>
+        <v>455229</v>
       </c>
       <c r="R30" t="n">
-        <v>6812351</v>
+        <v>6812759</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302750</v>
+        <v>122302773</v>
       </c>
       <c r="B31" t="n">
-        <v>78657</v>
+        <v>78044</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455083</v>
+        <v>454992</v>
       </c>
       <c r="R31" t="n">
-        <v>6812476</v>
+        <v>6812487</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302658</v>
+        <v>122302737</v>
       </c>
       <c r="B32" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455259</v>
+        <v>455267</v>
       </c>
       <c r="R32" t="n">
-        <v>6812731</v>
+        <v>6812474</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122302749</v>
+        <v>122302538</v>
       </c>
       <c r="B33" t="n">
-        <v>78657</v>
+        <v>79278</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455098</v>
+        <v>455290</v>
       </c>
       <c r="R33" t="n">
-        <v>6812474</v>
+        <v>6812727</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122302659</v>
+        <v>122302583</v>
       </c>
       <c r="B34" t="n">
-        <v>78657</v>
+        <v>78397</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455293</v>
+        <v>455177</v>
       </c>
       <c r="R34" t="n">
-        <v>6812728</v>
+        <v>6812448</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122302751</v>
+        <v>122302650</v>
       </c>
       <c r="B35" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454998</v>
+        <v>455089</v>
       </c>
       <c r="R35" t="n">
-        <v>6812459</v>
+        <v>6812828</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122302674</v>
+        <v>122302653</v>
       </c>
       <c r="B36" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455758</v>
+        <v>455173</v>
       </c>
       <c r="R36" t="n">
-        <v>6812559</v>
+        <v>6812786</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302752</v>
+        <v>122302669</v>
       </c>
       <c r="B37" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454985</v>
+        <v>455567</v>
       </c>
       <c r="R37" t="n">
-        <v>6812455</v>
+        <v>6812725</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302655</v>
+        <v>122302750</v>
       </c>
       <c r="B38" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455201</v>
+        <v>455083</v>
       </c>
       <c r="R38" t="n">
-        <v>6812767</v>
+        <v>6812476</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302753</v>
+        <v>122302657</v>
       </c>
       <c r="B39" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454977</v>
+        <v>455243</v>
       </c>
       <c r="R39" t="n">
-        <v>6812451</v>
+        <v>6812747</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,10 +4551,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122302537</v>
+        <v>122302659</v>
       </c>
       <c r="B40" t="n">
-        <v>79275</v>
+        <v>78660</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455203</v>
+        <v>455293</v>
       </c>
       <c r="R40" t="n">
-        <v>6812760</v>
+        <v>6812728</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302671</v>
+        <v>122302584</v>
       </c>
       <c r="B41" t="n">
-        <v>78657</v>
+        <v>78397</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455616</v>
+        <v>455165</v>
       </c>
       <c r="R41" t="n">
-        <v>6812570</v>
+        <v>6812417</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302724</v>
+        <v>122302753</v>
       </c>
       <c r="B42" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455449</v>
+        <v>454977</v>
       </c>
       <c r="R42" t="n">
-        <v>6812352</v>
+        <v>6812451</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -4857,10 +4857,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302726</v>
+        <v>122302724</v>
       </c>
       <c r="B43" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455407</v>
+        <v>455449</v>
       </c>
       <c r="R43" t="n">
-        <v>6812392</v>
+        <v>6812352</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302552</v>
+        <v>122302672</v>
       </c>
       <c r="B44" t="n">
-        <v>78691</v>
+        <v>78660</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455409</v>
+        <v>455638</v>
       </c>
       <c r="R44" t="n">
-        <v>6812375</v>
+        <v>6812544</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302670</v>
+        <v>122302652</v>
       </c>
       <c r="B45" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455615</v>
+        <v>455165</v>
       </c>
       <c r="R45" t="n">
-        <v>6812587</v>
+        <v>6812792</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122302737</v>
+        <v>122302743</v>
       </c>
       <c r="B46" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455267</v>
+        <v>455165</v>
       </c>
       <c r="R46" t="n">
-        <v>6812474</v>
+        <v>6812417</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122302584</v>
+        <v>122302654</v>
       </c>
       <c r="B47" t="n">
-        <v>78394</v>
+        <v>78660</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5281,21 +5281,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455165</v>
+        <v>455187</v>
       </c>
       <c r="R47" t="n">
-        <v>6812417</v>
+        <v>6812780</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,10 +5367,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302745</v>
+        <v>122302749</v>
       </c>
       <c r="B48" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455154</v>
+        <v>455098</v>
       </c>
       <c r="R48" t="n">
-        <v>6812449</v>
+        <v>6812474</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,10 +5469,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122302651</v>
+        <v>122302726</v>
       </c>
       <c r="B49" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455119</v>
+        <v>455407</v>
       </c>
       <c r="R49" t="n">
-        <v>6812817</v>
+        <v>6812392</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -5571,10 +5571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122302650</v>
+        <v>122302604</v>
       </c>
       <c r="B50" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455089</v>
+        <v>455405</v>
       </c>
       <c r="R50" t="n">
-        <v>6812828</v>
+        <v>6812359</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -5673,10 +5673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302743</v>
+        <v>122302744</v>
       </c>
       <c r="B51" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>455165</v>
       </c>
       <c r="R51" t="n">
-        <v>6812417</v>
+        <v>6812443</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302553</v>
+        <v>122302666</v>
       </c>
       <c r="B52" t="n">
-        <v>79246</v>
+        <v>78660</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5791,21 +5791,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455736</v>
+        <v>455428</v>
       </c>
       <c r="R52" t="n">
-        <v>6812556</v>
+        <v>6812747</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 61782-2024 artfynd.xlsx
+++ b/artfynd/A 61782-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302736</v>
+        <v>122302537</v>
       </c>
       <c r="B2" t="n">
-        <v>78660</v>
+        <v>79278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455295</v>
+        <v>455203</v>
       </c>
       <c r="R2" t="n">
-        <v>6812491</v>
+        <v>6812760</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302745</v>
+        <v>122302654</v>
       </c>
       <c r="B3" t="n">
         <v>78660</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455154</v>
+        <v>455187</v>
       </c>
       <c r="R3" t="n">
-        <v>6812449</v>
+        <v>6812780</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122302752</v>
+        <v>122302657</v>
       </c>
       <c r="B4" t="n">
         <v>78660</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454985</v>
+        <v>455243</v>
       </c>
       <c r="R4" t="n">
-        <v>6812455</v>
+        <v>6812747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122302658</v>
+        <v>122302603</v>
       </c>
       <c r="B5" t="n">
         <v>78660</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455259</v>
+        <v>455413</v>
       </c>
       <c r="R5" t="n">
-        <v>6812731</v>
+        <v>6812351</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122302674</v>
+        <v>122302725</v>
       </c>
       <c r="B6" t="n">
         <v>78660</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455758</v>
+        <v>455413</v>
       </c>
       <c r="R6" t="n">
-        <v>6812559</v>
+        <v>6812371</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122302553</v>
+        <v>122302585</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>78397</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455736</v>
+        <v>454995</v>
       </c>
       <c r="R7" t="n">
-        <v>6812556</v>
+        <v>6812454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122302671</v>
+        <v>122302743</v>
       </c>
       <c r="B8" t="n">
         <v>78660</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455616</v>
+        <v>455165</v>
       </c>
       <c r="R8" t="n">
-        <v>6812570</v>
+        <v>6812417</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122302751</v>
+        <v>122302672</v>
       </c>
       <c r="B9" t="n">
         <v>78660</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454998</v>
+        <v>455638</v>
       </c>
       <c r="R9" t="n">
-        <v>6812459</v>
+        <v>6812544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122302552</v>
+        <v>122302659</v>
       </c>
       <c r="B10" t="n">
-        <v>78694</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455409</v>
+        <v>455293</v>
       </c>
       <c r="R10" t="n">
-        <v>6812375</v>
+        <v>6812728</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122302651</v>
+        <v>122302553</v>
       </c>
       <c r="B11" t="n">
-        <v>78660</v>
+        <v>79249</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455119</v>
+        <v>455736</v>
       </c>
       <c r="R11" t="n">
-        <v>6812817</v>
+        <v>6812556</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122302655</v>
+        <v>122302754</v>
       </c>
       <c r="B12" t="n">
         <v>78660</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455201</v>
+        <v>454970</v>
       </c>
       <c r="R12" t="n">
-        <v>6812767</v>
+        <v>6812456</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122302665</v>
+        <v>122302658</v>
       </c>
       <c r="B13" t="n">
         <v>78660</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455420</v>
+        <v>455259</v>
       </c>
       <c r="R13" t="n">
-        <v>6812744</v>
+        <v>6812731</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122302727</v>
+        <v>122302750</v>
       </c>
       <c r="B14" t="n">
         <v>78660</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455408</v>
+        <v>455083</v>
       </c>
       <c r="R14" t="n">
-        <v>6812407</v>
+        <v>6812476</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122302747</v>
+        <v>122302666</v>
       </c>
       <c r="B16" t="n">
         <v>78660</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455137</v>
+        <v>455428</v>
       </c>
       <c r="R16" t="n">
-        <v>6812474</v>
+        <v>6812747</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122302673</v>
+        <v>122302746</v>
       </c>
       <c r="B17" t="n">
         <v>78660</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455747</v>
+        <v>455138</v>
       </c>
       <c r="R17" t="n">
-        <v>6812550</v>
+        <v>6812473</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122302603</v>
+        <v>122302747</v>
       </c>
       <c r="B18" t="n">
         <v>78660</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455413</v>
+        <v>455137</v>
       </c>
       <c r="R18" t="n">
-        <v>6812351</v>
+        <v>6812474</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122302725</v>
+        <v>122302605</v>
       </c>
       <c r="B19" t="n">
         <v>78660</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455413</v>
+        <v>455043</v>
       </c>
       <c r="R19" t="n">
-        <v>6812371</v>
+        <v>6812499</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122302585</v>
+        <v>122302552</v>
       </c>
       <c r="B20" t="n">
-        <v>78397</v>
+        <v>78694</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454995</v>
+        <v>455409</v>
       </c>
       <c r="R20" t="n">
-        <v>6812454</v>
+        <v>6812375</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122302748</v>
+        <v>122302604</v>
       </c>
       <c r="B21" t="n">
         <v>78660</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455119</v>
+        <v>455405</v>
       </c>
       <c r="R21" t="n">
-        <v>6812489</v>
+        <v>6812359</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122302668</v>
+        <v>122302652</v>
       </c>
       <c r="B22" t="n">
         <v>78660</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455485</v>
+        <v>455165</v>
       </c>
       <c r="R22" t="n">
-        <v>6812754</v>
+        <v>6812792</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122302667</v>
+        <v>122302751</v>
       </c>
       <c r="B23" t="n">
         <v>78660</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455438</v>
+        <v>454998</v>
       </c>
       <c r="R23" t="n">
-        <v>6812744</v>
+        <v>6812459</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122302594</v>
+        <v>122302773</v>
       </c>
       <c r="B24" t="n">
-        <v>78396</v>
+        <v>78044</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455177</v>
+        <v>454992</v>
       </c>
       <c r="R24" t="n">
-        <v>6812448</v>
+        <v>6812487</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122302746</v>
+        <v>122302584</v>
       </c>
       <c r="B25" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455138</v>
+        <v>455165</v>
       </c>
       <c r="R25" t="n">
-        <v>6812473</v>
+        <v>6812417</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122302605</v>
+        <v>122302737</v>
       </c>
       <c r="B26" t="n">
         <v>78660</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455043</v>
+        <v>455267</v>
       </c>
       <c r="R26" t="n">
-        <v>6812499</v>
+        <v>6812474</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,7 +3225,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122302754</v>
+        <v>122302655</v>
       </c>
       <c r="B27" t="n">
         <v>78660</v>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454970</v>
+        <v>455201</v>
       </c>
       <c r="R27" t="n">
-        <v>6812456</v>
+        <v>6812767</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122302537</v>
+        <v>122302727</v>
       </c>
       <c r="B28" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455203</v>
+        <v>455408</v>
       </c>
       <c r="R28" t="n">
-        <v>6812760</v>
+        <v>6812407</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3429,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122302579</v>
+        <v>122302651</v>
       </c>
       <c r="B29" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455212</v>
+        <v>455119</v>
       </c>
       <c r="R29" t="n">
-        <v>6812763</v>
+        <v>6812817</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122302656</v>
+        <v>122302650</v>
       </c>
       <c r="B30" t="n">
         <v>78660</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455229</v>
+        <v>455089</v>
       </c>
       <c r="R30" t="n">
-        <v>6812759</v>
+        <v>6812828</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122302773</v>
+        <v>122302538</v>
       </c>
       <c r="B31" t="n">
-        <v>78044</v>
+        <v>79278</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3649,21 +3649,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454992</v>
+        <v>455290</v>
       </c>
       <c r="R31" t="n">
-        <v>6812487</v>
+        <v>6812727</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122302737</v>
+        <v>122302583</v>
       </c>
       <c r="B32" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455267</v>
+        <v>455177</v>
       </c>
       <c r="R32" t="n">
-        <v>6812474</v>
+        <v>6812448</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122302538</v>
+        <v>122302736</v>
       </c>
       <c r="B33" t="n">
-        <v>79278</v>
+        <v>78660</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3853,21 +3853,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455290</v>
+        <v>455295</v>
       </c>
       <c r="R33" t="n">
-        <v>6812727</v>
+        <v>6812491</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122302583</v>
+        <v>122302748</v>
       </c>
       <c r="B34" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,21 +3955,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455177</v>
+        <v>455119</v>
       </c>
       <c r="R34" t="n">
-        <v>6812448</v>
+        <v>6812489</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122302650</v>
+        <v>122302668</v>
       </c>
       <c r="B35" t="n">
         <v>78660</v>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455089</v>
+        <v>455485</v>
       </c>
       <c r="R35" t="n">
-        <v>6812828</v>
+        <v>6812754</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122302653</v>
+        <v>122302753</v>
       </c>
       <c r="B36" t="n">
         <v>78660</v>
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455173</v>
+        <v>454977</v>
       </c>
       <c r="R36" t="n">
-        <v>6812786</v>
+        <v>6812451</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122302669</v>
+        <v>122302656</v>
       </c>
       <c r="B37" t="n">
         <v>78660</v>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455567</v>
+        <v>455229</v>
       </c>
       <c r="R37" t="n">
-        <v>6812725</v>
+        <v>6812759</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122302750</v>
+        <v>122302667</v>
       </c>
       <c r="B38" t="n">
         <v>78660</v>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455083</v>
+        <v>455438</v>
       </c>
       <c r="R38" t="n">
-        <v>6812476</v>
+        <v>6812744</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,7 +4449,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122302657</v>
+        <v>122302724</v>
       </c>
       <c r="B39" t="n">
         <v>78660</v>
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455243</v>
+        <v>455449</v>
       </c>
       <c r="R39" t="n">
-        <v>6812747</v>
+        <v>6812352</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -4551,7 +4551,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122302659</v>
+        <v>122302673</v>
       </c>
       <c r="B40" t="n">
         <v>78660</v>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455293</v>
+        <v>455747</v>
       </c>
       <c r="R40" t="n">
-        <v>6812728</v>
+        <v>6812550</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,10 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122302584</v>
+        <v>122302726</v>
       </c>
       <c r="B41" t="n">
-        <v>78397</v>
+        <v>78660</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455165</v>
+        <v>455407</v>
       </c>
       <c r="R41" t="n">
-        <v>6812417</v>
+        <v>6812392</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4755,10 +4755,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122302753</v>
+        <v>122302594</v>
       </c>
       <c r="B42" t="n">
-        <v>78660</v>
+        <v>78396</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,21 +4771,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454977</v>
+        <v>455177</v>
       </c>
       <c r="R42" t="n">
-        <v>6812451</v>
+        <v>6812448</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122302724</v>
+        <v>122302674</v>
       </c>
       <c r="B43" t="n">
         <v>78660</v>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455449</v>
+        <v>455758</v>
       </c>
       <c r="R43" t="n">
-        <v>6812352</v>
+        <v>6812559</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -4959,7 +4959,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122302672</v>
+        <v>122302669</v>
       </c>
       <c r="B44" t="n">
         <v>78660</v>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455638</v>
+        <v>455567</v>
       </c>
       <c r="R44" t="n">
-        <v>6812544</v>
+        <v>6812725</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122302652</v>
+        <v>122302579</v>
       </c>
       <c r="B45" t="n">
-        <v>78660</v>
+        <v>78397</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,21 +5077,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455165</v>
+        <v>455212</v>
       </c>
       <c r="R45" t="n">
-        <v>6812792</v>
+        <v>6812763</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122302743</v>
+        <v>122302752</v>
       </c>
       <c r="B46" t="n">
         <v>78660</v>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455165</v>
+        <v>454985</v>
       </c>
       <c r="R46" t="n">
-        <v>6812417</v>
+        <v>6812455</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122302654</v>
+        <v>122302671</v>
       </c>
       <c r="B47" t="n">
         <v>78660</v>
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455187</v>
+        <v>455616</v>
       </c>
       <c r="R47" t="n">
-        <v>6812780</v>
+        <v>6812570</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,7 +5367,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122302749</v>
+        <v>122302665</v>
       </c>
       <c r="B48" t="n">
         <v>78660</v>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455098</v>
+        <v>455420</v>
       </c>
       <c r="R48" t="n">
-        <v>6812474</v>
+        <v>6812744</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122302726</v>
+        <v>122302744</v>
       </c>
       <c r="B49" t="n">
         <v>78660</v>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455407</v>
+        <v>455165</v>
       </c>
       <c r="R49" t="n">
-        <v>6812392</v>
+        <v>6812443</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -5571,7 +5571,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122302604</v>
+        <v>122302745</v>
       </c>
       <c r="B50" t="n">
         <v>78660</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455405</v>
+        <v>455154</v>
       </c>
       <c r="R50" t="n">
-        <v>6812359</v>
+        <v>6812449</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -5673,7 +5673,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122302744</v>
+        <v>122302749</v>
       </c>
       <c r="B51" t="n">
         <v>78660</v>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455165</v>
+        <v>455098</v>
       </c>
       <c r="R51" t="n">
-        <v>6812443</v>
+        <v>6812474</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,7 +5775,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122302666</v>
+        <v>122302653</v>
       </c>
       <c r="B52" t="n">
         <v>78660</v>
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455428</v>
+        <v>455173</v>
       </c>
       <c r="R52" t="n">
-        <v>6812747</v>
+        <v>6812786</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
